--- a/outputs/validation_truss_nodal_loads.xlsx
+++ b/outputs/validation_truss_nodal_loads.xlsx
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000514519309048216</v>
+        <v>0.0005145193090482427</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000514519309048216</v>
+        <v>0.0005145193090482427</v>
       </c>
     </row>
     <row r="4">
@@ -573,13 +573,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005021620520047466</v>
+        <v>0.005021620520047738</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008381677031599073</v>
+        <v>0.008381677031599621</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.01186215091270229</v>
+        <v>-0.01186215091270305</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01536814259385697</v>
+        <v>0.01536814259385795</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005111801563984705</v>
+        <v>0.005111801563984978</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.006399919298218829</v>
+        <v>-0.006399919298219385</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00702966564617685</v>
+        <v>0.007029665646177609</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01079377975272375</v>
+        <v>0.01079377975272471</v>
       </c>
     </row>
     <row r="6">
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01575698001207688</v>
+        <v>0.01575698001207803</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02141662733484937</v>
+        <v>0.02141662733485085</v>
       </c>
     </row>
     <row r="7">
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.015656775540507</v>
+        <v>0.01565677554050815</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0182560620376863</v>
+        <v>0.01825606203768776</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01037637654107239</v>
+        <v>0.01037637654107306</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01543191053294733</v>
+        <v>-0.01543191053294826</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02277298983743186</v>
+        <v>0.02277298983743323</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.00793200500685427</v>
+        <v>-0.007932005006854951</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00856876992556288</v>
+        <v>0.008568769925563794</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01768668104421645</v>
+        <v>0.01768668104421776</v>
       </c>
     </row>
     <row r="10">
@@ -783,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.05467606590323344</v>
+        <v>0.05467606590323749</v>
       </c>
     </row>
     <row r="11">
@@ -818,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05054266662275082</v>
+        <v>0.05054266662275473</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="G11" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.05196847286834083</v>
+        <v>0.0519684728683449</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06013483678090194</v>
+        <v>0.06013483678090634</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006930127646340921</v>
+        <v>0.006930127646341633</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01678443355793183</v>
+        <v>-0.01678443355793261</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06281673721008536</v>
+        <v>0.06281673721008986</v>
       </c>
     </row>
     <row r="13">
@@ -888,13 +888,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06091050489581464</v>
+        <v>0.06091050489581906</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.007727155750850413</v>
+        <v>-0.007727155750851131</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006973120948370765</v>
+        <v>0.006973120948371539</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06179338927766923</v>
+        <v>0.06179338927767376</v>
       </c>
     </row>
     <row r="14">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09735868234219669</v>
+        <v>0.09735868234220449</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09826545067236638</v>
+        <v>0.09826545067237424</v>
       </c>
     </row>
     <row r="15">
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09737080707456244</v>
+        <v>0.09737080707457024</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01060651122144798</v>
+        <v>-0.01060651122144902</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09794678223730661</v>
+        <v>0.09794678223731448</v>
       </c>
     </row>
   </sheetData>
@@ -1035,13 +1035,13 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09826545067236638</v>
+        <v>0.09826545067237424</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09735868234219669</v>
+        <v>0.09735868234220449</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1057,13 +1057,13 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09737080707456244</v>
+        <v>0.09737080707457024</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09737080707456244</v>
+        <v>0.09737080707457024</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01060651122144798</v>
+        <v>-0.01060651122144902</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1079,13 +1079,13 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09735868234219669</v>
+        <v>0.09735868234220449</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1101,16 +1101,16 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
     </row>
   </sheetData>
@@ -1154,13 +1154,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-99.99999999999355</v>
+        <v>-99.99999999999871</v>
       </c>
       <c r="C2" t="n">
-        <v>-449.9999999999666</v>
+        <v>-449.9999999999975</v>
       </c>
       <c r="D2" t="n">
-        <v>-51.93512595216902</v>
+        <v>-51.93512595217241</v>
       </c>
     </row>
     <row r="3">
@@ -1169,10 +1169,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>449.9999999999662</v>
+        <v>449.9999999999976</v>
       </c>
       <c r="D3" t="n">
-        <v>76.93512595216902</v>
+        <v>76.93512595217273</v>
       </c>
     </row>
     <row r="4">
@@ -1182,7 +1182,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>65.33258557372574</v>
+        <v>65.33258557373006</v>
       </c>
     </row>
     <row r="5">
@@ -1192,7 +1192,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>9.66741442627449</v>
+        <v>9.667414426270284</v>
       </c>
     </row>
   </sheetData>
@@ -1275,16 +1275,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001047920711633271</v>
+        <v>0.001047920711633349</v>
       </c>
       <c r="H2" t="n">
-        <v>293.4177992573158</v>
+        <v>293.4177992573378</v>
       </c>
       <c r="I2" t="n">
-        <v>73354.44981432894</v>
+        <v>73354.44981433444</v>
       </c>
     </row>
     <row r="3">
@@ -1306,16 +1306,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001327669779330199</v>
+        <v>0.00132766977933029</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002555101681637406</v>
+        <v>0.0002555101681637581</v>
       </c>
       <c r="H3" t="n">
-        <v>71.54284708584736</v>
+        <v>71.54284708585226</v>
       </c>
       <c r="I3" t="n">
-        <v>17885.71177146184</v>
+        <v>17885.71177146307</v>
       </c>
     </row>
     <row r="4">
@@ -1337,16 +1337,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.469446951953614e-18</v>
+        <v>-1.734723475976807e-18</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.156482317317871e-18</v>
+        <v>-5.782411586589357e-19</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.23815048849004e-13</v>
+        <v>-1.61907524424502e-13</v>
       </c>
       <c r="I4" t="n">
-        <v>-8.095376221225099e-11</v>
+        <v>-4.04768811061255e-11</v>
       </c>
     </row>
     <row r="5">
@@ -1368,16 +1368,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.74193620022723e-05</v>
+        <v>-5.741936200224455e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.105036136956949e-05</v>
+        <v>-1.105036136956415e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.094101183479459</v>
+        <v>-3.094101183477963</v>
       </c>
       <c r="I5" t="n">
-        <v>-773.5252958698646</v>
+        <v>-773.5252958694907</v>
       </c>
     </row>
     <row r="6">
@@ -1399,16 +1399,16 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>1.734723475976807e-18</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.891205793294678e-19</v>
+        <v>5.782411586589357e-19</v>
       </c>
       <c r="H6" t="n">
-        <v>8.095376221225099e-14</v>
+        <v>1.61907524424502e-13</v>
       </c>
       <c r="I6" t="n">
-        <v>2.023844055306275e-11</v>
+        <v>4.04768811061255e-11</v>
       </c>
     </row>
     <row r="7">
@@ -1430,16 +1430,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003978061608659943</v>
+        <v>0.003978061608660286</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0006630102681099906</v>
+        <v>0.0006630102681100476</v>
       </c>
       <c r="H7" t="n">
-        <v>185.6428750707973</v>
+        <v>185.6428750708133</v>
       </c>
       <c r="I7" t="n">
-        <v>46410.71876769933</v>
+        <v>46410.71876770334</v>
       </c>
     </row>
     <row r="8">
@@ -1461,16 +1461,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001855768722395238</v>
+        <v>0.001855768722395242</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000309294787065873</v>
+        <v>0.0003092947870658736</v>
       </c>
       <c r="H8" t="n">
-        <v>86.60254037844444</v>
+        <v>86.6025403784446</v>
       </c>
       <c r="I8" t="n">
-        <v>21650.63509461111</v>
+        <v>21650.63509461115</v>
       </c>
     </row>
     <row r="9">
@@ -1492,16 +1492,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.002308277578109251</v>
+        <v>-0.002308277578109291</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0004442282270285844</v>
+        <v>-0.0004442282270285921</v>
       </c>
       <c r="H9" t="n">
-        <v>-124.3839035680036</v>
+        <v>-124.3839035680058</v>
       </c>
       <c r="I9" t="n">
-        <v>-31095.97589200091</v>
+        <v>-31095.97589200145</v>
       </c>
     </row>
     <row r="10">
@@ -1523,16 +1523,16 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0009278843611976173</v>
+        <v>-0.0009278843611976138</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0003092947870658724</v>
+        <v>-0.0003092947870658713</v>
       </c>
       <c r="H10" t="n">
-        <v>-86.60254037844427</v>
+        <v>-86.60254037844395</v>
       </c>
       <c r="I10" t="n">
-        <v>-21650.63509461107</v>
+        <v>-21650.63509461099</v>
       </c>
     </row>
     <row r="11">
@@ -1554,16 +1554,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003053038991792902</v>
+        <v>0.003053038991793114</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0005088398319654837</v>
+        <v>0.000508839831965519</v>
       </c>
       <c r="H11" t="n">
-        <v>142.4751529503354</v>
+        <v>142.4751529503453</v>
       </c>
       <c r="I11" t="n">
-        <v>35618.78823758385</v>
+        <v>35618.78823758633</v>
       </c>
     </row>
     <row r="12">
@@ -1585,16 +1585,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.00285961589105215</v>
+        <v>-0.00285961589105227</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0005503333348259634</v>
+        <v>-0.0005503333348259865</v>
       </c>
       <c r="H12" t="n">
-        <v>-154.0933337512698</v>
+        <v>-154.0933337512762</v>
       </c>
       <c r="I12" t="n">
-        <v>-38523.33343781744</v>
+        <v>-38523.33343781906</v>
       </c>
     </row>
     <row r="13">
@@ -1616,16 +1616,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009721764579191486</v>
+        <v>-0.0009721764579192282</v>
       </c>
       <c r="H13" t="n">
-        <v>-272.2094082173616</v>
+        <v>-272.2094082173839</v>
       </c>
       <c r="I13" t="n">
-        <v>-68052.3520543404</v>
+        <v>-68052.35205434597</v>
       </c>
     </row>
     <row r="14">
@@ -1647,16 +1647,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.002027659871339357</v>
+        <v>-0.00202765987133946</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0003902233241809266</v>
+        <v>-0.0003902233241809464</v>
       </c>
       <c r="H14" t="n">
-        <v>-109.2625307706595</v>
+        <v>-109.262530770665</v>
       </c>
       <c r="I14" t="n">
-        <v>-27315.63269266486</v>
+        <v>-27315.63269266625</v>
       </c>
     </row>
     <row r="15">
@@ -1678,16 +1678,16 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>1.734723475976807e-18</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>5.782411586589357e-19</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.61907524424502e-13</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4.04768811061255e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1709,16 +1709,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0005572730047603597</v>
+        <v>-0.0005572730047603905</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0001072472397701684</v>
+        <v>-0.0001072472397701743</v>
       </c>
       <c r="H16" t="n">
-        <v>-30.02922713564716</v>
+        <v>-30.02922713564882</v>
       </c>
       <c r="I16" t="n">
-        <v>-7507.306783911789</v>
+        <v>-7507.306783912204</v>
       </c>
     </row>
     <row r="17">
@@ -1740,16 +1740,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.257674520083185e-17</v>
+        <v>-1.908195823574488e-17</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.096124200138642e-18</v>
+        <v>-3.180326372624146e-18</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.869147760388197e-13</v>
+        <v>-8.904913843347609e-13</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.467286940097049e-10</v>
+        <v>-2.226228460836902e-10</v>
       </c>
     </row>
     <row r="18">
@@ -1771,16 +1771,16 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.003378394181108487</v>
+        <v>-0.003378394181108829</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0005630656968514144</v>
+        <v>-0.0005630656968514716</v>
       </c>
       <c r="H18" t="n">
-        <v>-157.658395118396</v>
+        <v>-157.658395118412</v>
       </c>
       <c r="I18" t="n">
-        <v>-39414.59877959901</v>
+        <v>-39414.598779603</v>
       </c>
     </row>
     <row r="19">
@@ -1833,16 +1833,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0009752291482417377</v>
+        <v>0.0009752291482417793</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0001876829370863122</v>
+        <v>0.0001876829370863202</v>
       </c>
       <c r="H20" t="n">
-        <v>52.55122238416742</v>
+        <v>52.55122238416967</v>
       </c>
       <c r="I20" t="n">
-        <v>13137.80559604186</v>
+        <v>13137.80559604242</v>
       </c>
     </row>
     <row r="21">
@@ -1864,16 +1864,16 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>3.035766082959412e-18</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="G21" t="n">
-        <v>1.011922027653138e-18</v>
+        <v>1.156482317317871e-18</v>
       </c>
       <c r="H21" t="n">
-        <v>2.833381677428785e-13</v>
+        <v>3.23815048849004e-13</v>
       </c>
       <c r="I21" t="n">
-        <v>7.083454193571961e-11</v>
+        <v>8.095376221225099e-11</v>
       </c>
     </row>
     <row r="22">
@@ -1895,16 +1895,16 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.001395058292824604</v>
+        <v>-0.001395058292824818</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0002325097154707674</v>
+        <v>-0.0002325097154708029</v>
       </c>
       <c r="H22" t="n">
-        <v>-65.10272033181487</v>
+        <v>-65.10272033182481</v>
       </c>
       <c r="I22" t="n">
-        <v>-16275.68008295372</v>
+        <v>-16275.6800829562</v>
       </c>
     </row>
     <row r="23">
@@ -1926,16 +1926,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0009929654901221913</v>
+        <v>0.0009929654901223023</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001910962976726853</v>
+        <v>0.0001910962976727066</v>
       </c>
       <c r="H23" t="n">
-        <v>53.50696334835187</v>
+        <v>53.50696334835786</v>
       </c>
       <c r="I23" t="n">
-        <v>13376.74083708797</v>
+        <v>13376.74083708946</v>
       </c>
     </row>
     <row r="24">
@@ -1957,16 +1957,16 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.000514519309048216</v>
+        <v>0.0005145193090482427</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0001715064363494053</v>
+        <v>0.0001715064363494142</v>
       </c>
       <c r="H24" t="n">
-        <v>48.02180217783349</v>
+        <v>48.02180217783598</v>
       </c>
       <c r="I24" t="n">
-        <v>12005.45054445837</v>
+        <v>12005.45054445899</v>
       </c>
     </row>
     <row r="25">
@@ -1988,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>9.018104393723921e-05</v>
+        <v>9.018104393724007e-05</v>
       </c>
       <c r="G25" t="n">
-        <v>3.006034797907974e-05</v>
+        <v>3.006034797908002e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>8.416897434142326</v>
+        <v>8.416897434142406</v>
       </c>
       <c r="I25" t="n">
-        <v>2104.224358535581</v>
+        <v>2104.224358535601</v>
       </c>
     </row>
     <row r="26">
@@ -2050,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0001393187144937812</v>
+        <v>0.000139318714493783</v>
       </c>
       <c r="G27" t="n">
-        <v>4.643957149792708e-05</v>
+        <v>4.643957149792766e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>13.00308001941958</v>
+        <v>13.00308001941974</v>
       </c>
       <c r="I27" t="n">
-        <v>3250.770004854895</v>
+        <v>3250.770004854935</v>
       </c>
     </row>
     <row r="28">
@@ -2112,16 +2112,16 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0007756681149127045</v>
+        <v>0.0007756681149127184</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0002585560383042348</v>
+        <v>0.0002585560383042395</v>
       </c>
       <c r="H29" t="n">
-        <v>72.39569072518576</v>
+        <v>72.39569072518705</v>
       </c>
       <c r="I29" t="n">
-        <v>18098.92268129644</v>
+        <v>18098.92268129676</v>
       </c>
     </row>
     <row r="30">
@@ -2174,16 +2174,16 @@
         <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0007998958231781837</v>
+        <v>0.0007998958231782297</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0001333159705296973</v>
+        <v>0.0001333159705297049</v>
       </c>
       <c r="H31" t="n">
-        <v>37.32847174831524</v>
+        <v>37.32847174831738</v>
       </c>
       <c r="I31" t="n">
-        <v>9332.117937078809</v>
+        <v>9332.117937079345</v>
       </c>
     </row>
     <row r="32">
@@ -2205,16 +2205,16 @@
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.001103754848762794</v>
+        <v>-0.001103754848762836</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0001839591414604656</v>
+        <v>-0.0001839591414604727</v>
       </c>
       <c r="H32" t="n">
-        <v>-51.50855960893036</v>
+        <v>-51.50855960893236</v>
       </c>
       <c r="I32" t="n">
-        <v>-12877.13990223259</v>
+        <v>-12877.13990223309</v>
       </c>
     </row>
     <row r="33">
@@ -2236,16 +2236,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F33" t="n">
-        <v>0.001784676532928702</v>
+        <v>0.001784676532928786</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0002660438696984812</v>
+        <v>0.0002660438696984938</v>
       </c>
       <c r="H33" t="n">
-        <v>74.49228351557475</v>
+        <v>74.49228351557826</v>
       </c>
       <c r="I33" t="n">
-        <v>18623.07087889369</v>
+        <v>18623.07087889457</v>
       </c>
     </row>
     <row r="34">
@@ -2267,16 +2267,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.001192902984287592</v>
+        <v>-0.00119290298428767</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0001778274775619612</v>
+        <v>-0.0001778274775619729</v>
       </c>
       <c r="H34" t="n">
-        <v>-49.79169371734914</v>
+        <v>-49.7916937173524</v>
       </c>
       <c r="I34" t="n">
-        <v>-12447.92342933728</v>
+        <v>-12447.9234293381</v>
       </c>
     </row>
     <row r="35">
@@ -2298,16 +2298,16 @@
         <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0007430306730138352</v>
+        <v>0.0007430306730138777</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0001238384455023059</v>
+        <v>0.0001238384455023129</v>
       </c>
       <c r="H35" t="n">
-        <v>34.67476474064564</v>
+        <v>34.67476474064762</v>
       </c>
       <c r="I35" t="n">
-        <v>8668.69118516141</v>
+        <v>8668.691185161906</v>
       </c>
     </row>
     <row r="36">
@@ -2329,16 +2329,16 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.001160619998927145</v>
+        <v>-0.00116061999892719</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0001934366664878575</v>
+        <v>-0.000193436666487865</v>
       </c>
       <c r="H36" t="n">
-        <v>-54.16226661660009</v>
+        <v>-54.1622666166022</v>
       </c>
       <c r="I36" t="n">
-        <v>-13540.56665415002</v>
+        <v>-13540.56665415055</v>
       </c>
     </row>
     <row r="37">
@@ -2360,16 +2360,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F37" t="n">
-        <v>0.001693925342137009</v>
+        <v>0.001693925342137087</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0002525154809218626</v>
+        <v>0.0002525154809218743</v>
       </c>
       <c r="H37" t="n">
-        <v>70.70433465812155</v>
+        <v>70.70433465812481</v>
       </c>
       <c r="I37" t="n">
-        <v>17676.08366453039</v>
+        <v>17676.0836645312</v>
       </c>
     </row>
     <row r="38">
@@ -2391,16 +2391,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.001283654175079302</v>
+        <v>-0.001283654175079384</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0001913558663385824</v>
+        <v>-0.0001913558663385945</v>
       </c>
       <c r="H38" t="n">
-        <v>-53.57964257480307</v>
+        <v>-53.57964257480648</v>
       </c>
       <c r="I38" t="n">
-        <v>-13394.91064370077</v>
+        <v>-13394.91064370162</v>
       </c>
     </row>
     <row r="39">
@@ -2422,16 +2422,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0006033451409519983</v>
+        <v>0.0006033451409520503</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0001005575234919997</v>
+        <v>0.0001005575234920084</v>
       </c>
       <c r="H39" t="n">
-        <v>28.15610657775992</v>
+        <v>28.15610657776235</v>
       </c>
       <c r="I39" t="n">
-        <v>7039.026644439979</v>
+        <v>7039.026644440587</v>
       </c>
     </row>
     <row r="40">
@@ -2453,16 +2453,16 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.001300305530988977</v>
+        <v>-0.001300305530989022</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0002167175884981628</v>
+        <v>-0.0002167175884981703</v>
       </c>
       <c r="H40" t="n">
-        <v>-60.68092477948557</v>
+        <v>-60.68092477948768</v>
       </c>
       <c r="I40" t="n">
-        <v>-15170.23119487139</v>
+        <v>-15170.23119487192</v>
       </c>
     </row>
     <row r="41">
@@ -2484,16 +2484,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F41" t="n">
-        <v>0.002192334998998541</v>
+        <v>0.002192334998998638</v>
       </c>
       <c r="G41" t="n">
-        <v>0.000326814005814178</v>
+        <v>0.0003268140058141925</v>
       </c>
       <c r="H41" t="n">
-        <v>91.50792162796985</v>
+        <v>91.50792162797391</v>
       </c>
       <c r="I41" t="n">
-        <v>22876.98040699246</v>
+        <v>22876.98040699348</v>
       </c>
     </row>
     <row r="42">
@@ -2515,16 +2515,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.0007852445182178411</v>
+        <v>-0.0007852445182179382</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.0001170573414462776</v>
+        <v>-0.0001170573414462921</v>
       </c>
       <c r="H42" t="n">
-        <v>-32.77605560495774</v>
+        <v>-32.7760556049618</v>
       </c>
       <c r="I42" t="n">
-        <v>-8194.013901239436</v>
+        <v>-8194.013901240449</v>
       </c>
     </row>
     <row r="43">
@@ -2546,16 +2546,16 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.001802366928661925</v>
+        <v>-0.001802366928661869</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.0003003944881103208</v>
+        <v>-0.0003003944881103116</v>
       </c>
       <c r="H43" t="n">
-        <v>-84.11045667088982</v>
+        <v>-84.11045667088723</v>
       </c>
       <c r="I43" t="n">
-        <v>-21027.61416772246</v>
+        <v>-21027.61416772181</v>
       </c>
     </row>
     <row r="44">
@@ -2577,16 +2577,16 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0005796966851113958</v>
+        <v>0.0005796966851113541</v>
       </c>
       <c r="G44" t="n">
-        <v>9.661611418523262e-05</v>
+        <v>9.661611418522569e-05</v>
       </c>
       <c r="H44" t="n">
-        <v>27.05251197186513</v>
+        <v>27.05251197186319</v>
       </c>
       <c r="I44" t="n">
-        <v>6763.127992966283</v>
+        <v>6763.127992965799</v>
       </c>
     </row>
   </sheetData>
@@ -2829,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>293.4177992573158</v>
+        <v>293.4177992573378</v>
       </c>
       <c r="F2" t="n">
-        <v>73354.44981432894</v>
+        <v>73354.44981433444</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01575698001207688</v>
+        <v>0.01575698001207803</v>
       </c>
       <c r="N2" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.01575698001207688</v>
+        <v>-0.01575698001207803</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-293.4177992573159</v>
+        <v>-293.4177992573379</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>293.4177992573159</v>
+        <v>293.4177992573379</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E3" t="n">
-        <v>71.54284708584736</v>
+        <v>71.54284708585226</v>
       </c>
       <c r="F3" t="n">
-        <v>17885.71177146184</v>
+        <v>17885.71177146307</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.005021620520047466</v>
+        <v>0.005021620520047738</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008381677031599073</v>
+        <v>0.008381677031599621</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.01186215091270229</v>
+        <v>-0.01186215091270305</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001327669779330199</v>
+        <v>0.00132766977933029</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01446376254972448</v>
+        <v>0.01446376254972542</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.005021620520047466</v>
+        <v>-0.005021620520047738</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-71.54284708584736</v>
+        <v>-71.54284708585226</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>71.54284708584736</v>
+        <v>71.54284708585226</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.23815048849004e-13</v>
+        <v>-1.61907524424502e-13</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.095376221225099e-11</v>
+        <v>-4.04768811061255e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005021620520047466</v>
+        <v>0.005021620520047738</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008381677031599073</v>
+        <v>0.008381677031599621</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01186215091270229</v>
+        <v>-0.01186215091270305</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01575698001207688</v>
+        <v>0.01575698001207803</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01446376254972448</v>
+        <v>0.01446376254972542</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0013276697793302</v>
+        <v>0.001327669779330291</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005021620520047466</v>
+        <v>0.005021620520047738</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01446376254972448</v>
+        <v>0.01446376254972542</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.001090449542168018</v>
+        <v>-0.001090449542168017</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01575698001207688</v>
+        <v>0.01575698001207803</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.094101183479459</v>
+        <v>-3.094101183477963</v>
       </c>
       <c r="F5" t="n">
-        <v>-773.5252958698646</v>
+        <v>-773.5252958694907</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005021620520047466</v>
+        <v>0.005021620520047738</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008381677031599073</v>
+        <v>0.008381677031599621</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01186215091270229</v>
+        <v>-0.01186215091270305</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01037637654107239</v>
+        <v>0.01037637654107306</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01543191053294733</v>
+        <v>-0.01543191053294826</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001327669779330199</v>
+        <v>0.00132766977933029</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01446376254972448</v>
+        <v>0.01446376254972542</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.005021620520047466</v>
+        <v>-0.005021620520047738</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001270250417327927</v>
+        <v>0.001270250417328046</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01855261482099724</v>
+        <v>0.01855261482099838</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.01314518974061487</v>
+        <v>-0.01314518974061562</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.094101183479466</v>
+        <v>3.09410118347796</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-3.094101183479466</v>
+        <v>-3.09410118347796</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>8.095376221225099e-14</v>
+        <v>1.61907524424502e-13</v>
       </c>
       <c r="F6" t="n">
-        <v>2.023844055306275e-11</v>
+        <v>4.04768811061255e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01575698001207688</v>
+        <v>0.01575698001207803</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01037637654107239</v>
+        <v>0.01037637654107306</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01543191053294733</v>
+        <v>-0.01543191053294826</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.008176238279924853</v>
+        <v>-0.008176238279925323</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01198076103128337</v>
+        <v>0.01198076103128419</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.01575698001207688</v>
+        <v>-0.01575698001207803</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3401,13 +3401,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.008176238279924851</v>
+        <v>-0.00817623827992532</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01670216095027526</v>
+        <v>0.01670216095027631</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.01314518974061487</v>
+        <v>-0.01314518974061562</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>185.6428750707973</v>
+        <v>185.6428750708133</v>
       </c>
       <c r="F7" t="n">
-        <v>46410.71876769933</v>
+        <v>46410.71876770334</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01575698001207688</v>
+        <v>0.01575698001207803</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3493,13 +3493,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3511,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.01575698001207688</v>
+        <v>-0.01575698001207803</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3529,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.05072440278753466</v>
+        <v>-0.05072440278753856</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-185.6428750707974</v>
+        <v>-185.6428750708134</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>185.6428750707974</v>
+        <v>185.6428750708134</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>86.60254037844444</v>
+        <v>86.6025403784446</v>
       </c>
       <c r="F8" t="n">
-        <v>21650.63509461111</v>
+        <v>21650.63509461115</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01037637654107239</v>
+        <v>0.01037637654107306</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01543191053294733</v>
+        <v>-0.01543191053294826</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01855261482099724</v>
+        <v>0.01855261482099838</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001270250417327929</v>
+        <v>0.001270250417328048</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02040838354339248</v>
+        <v>0.02040838354339362</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.089180813292691e-05</v>
+        <v>7.089180813320793e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-86.60254037844447</v>
+        <v>-86.6025403784447</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>86.60254037844447</v>
+        <v>86.6025403784447</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>-124.3839035680036</v>
+        <v>-124.3839035680058</v>
       </c>
       <c r="F9" t="n">
-        <v>-31095.97589200091</v>
+        <v>-31095.97589200145</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01037637654107239</v>
+        <v>0.01037637654107306</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01543191053294733</v>
+        <v>-0.01543191053294826</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06013483678090194</v>
+        <v>0.06013483678090634</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006930127646340921</v>
+        <v>0.006930127646341633</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.01678443355793183</v>
+        <v>-0.01678443355793261</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01670216095027526</v>
+        <v>0.01670216095027631</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.00817623827992485</v>
+        <v>-0.008176238279925318</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01439388337216601</v>
+        <v>0.01439388337216702</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.01107068202613053</v>
+        <v>-0.01107068202613085</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.06013483678090194</v>
+        <v>0.06013483678090634</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>124.3839035680037</v>
+        <v>124.3839035680058</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-124.3839035680037</v>
+        <v>-124.3839035680058</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3853,19 +3853,19 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>-86.60254037844427</v>
+        <v>-86.60254037844395</v>
       </c>
       <c r="F10" t="n">
-        <v>-21650.63509461107</v>
+        <v>-21650.63509461099</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3877,13 +3877,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06013483678090194</v>
+        <v>0.06013483678090634</v>
       </c>
       <c r="N10" t="n">
-        <v>0.006930127646340921</v>
+        <v>0.006930127646341633</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.01678443355793183</v>
+        <v>-0.01678443355793261</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.01014279766493292</v>
+        <v>-0.01014279766493324</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01770962450282063</v>
+        <v>0.01770962450282176</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.05072440278753466</v>
+        <v>-0.05072440278753856</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3913,13 +3913,13 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.01107068202613053</v>
+        <v>-0.01107068202613086</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01439388337216601</v>
+        <v>0.01439388337216702</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.06013483678090194</v>
+        <v>-0.06013483678090634</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>86.60254037844436</v>
+        <v>86.6025403784439</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-86.60254037844436</v>
+        <v>-86.6025403784439</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>142.4751529503354</v>
+        <v>142.4751529503453</v>
       </c>
       <c r="F11" t="n">
-        <v>35618.78823758385</v>
+        <v>35618.78823758633</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.09735868234219669</v>
+        <v>0.09735868234220449</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.05072440278753466</v>
+        <v>-0.05072440278753856</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.09735868234219669</v>
+        <v>-0.09735868234220449</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-142.4751529503355</v>
+        <v>-142.4751529503454</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>142.4751529503355</v>
+        <v>142.4751529503454</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4109,19 +4109,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E12" t="n">
-        <v>-154.0933337512698</v>
+        <v>-154.0933337512762</v>
       </c>
       <c r="F12" t="n">
-        <v>-38523.33343781744</v>
+        <v>-38523.33343781906</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06013483678090194</v>
+        <v>0.06013483678090634</v>
       </c>
       <c r="H12" t="n">
-        <v>0.006930127646340921</v>
+        <v>0.006930127646341633</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01678443355793183</v>
+        <v>-0.01678443355793261</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09735868234219669</v>
+        <v>0.09735868234220449</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -4151,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01439388337216601</v>
+        <v>0.01439388337216702</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.01107068202613053</v>
+        <v>-0.01107068202613085</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06013483678090194</v>
+        <v>0.06013483678090634</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.01153426748111386</v>
+        <v>0.01153426748111475</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.006659312435126235</v>
+        <v>0.006659312435126748</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.09735868234219669</v>
+        <v>0.09735868234220449</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>154.0933337512697</v>
+        <v>154.0933337512762</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-154.0933337512697</v>
+        <v>-154.0933337512762</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4237,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>-272.2094082173616</v>
+        <v>-272.2094082173839</v>
       </c>
       <c r="F13" t="n">
-        <v>-68052.3520543404</v>
+        <v>-68052.35205434597</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000514519309048216</v>
+        <v>0.0005145193090482427</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.015656775540507</v>
+        <v>0.01565677554050815</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="O13" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.000514519309048216</v>
+        <v>-0.0005145193090482427</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.015656775540507</v>
+        <v>-0.01565677554050815</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>272.2094082173617</v>
+        <v>272.209408217384</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-272.2094082173617</v>
+        <v>-272.209408217384</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E14" t="n">
-        <v>-109.2625307706595</v>
+        <v>-109.262530770665</v>
       </c>
       <c r="F14" t="n">
-        <v>-27315.63269266486</v>
+        <v>-27315.63269266625</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000514519309048216</v>
+        <v>0.0005145193090482427</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.005111801563984705</v>
+        <v>0.005111801563984978</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.006399919298218829</v>
+        <v>-0.006399919298219385</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00702966564617685</v>
+        <v>0.007029665646177609</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.000514519309048216</v>
+        <v>-0.0005145193090482427</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.002027659871339357</v>
+        <v>-0.00202765987133946</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.009287828678809317</v>
+        <v>-0.009287828678810253</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.005111801563984705</v>
+        <v>-0.005111801563984978</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>109.2625307706595</v>
+        <v>109.262530770665</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-109.2625307706595</v>
+        <v>-109.262530770665</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -4493,19 +4493,19 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1.61907524424502e-13</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>4.04768811061255e-11</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.005111801563984705</v>
+        <v>0.005111801563984978</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.006399919298218829</v>
+        <v>-0.006399919298219385</v>
       </c>
       <c r="I15" t="n">
-        <v>0.00702966564617685</v>
+        <v>0.007029665646177609</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.015656775540507</v>
+        <v>0.01565677554050815</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="O15" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -4535,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.009287828678809319</v>
+        <v>-0.009287828678810253</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.002027659871339357</v>
+        <v>-0.00202765987133946</v>
       </c>
       <c r="U15" t="n">
-        <v>0.005111801563984705</v>
+        <v>0.005111801563984978</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.009287828678809317</v>
+        <v>-0.009287828678810253</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.001373105688255563</v>
+        <v>-0.001373105688255575</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.015656775540507</v>
+        <v>0.01565677554050815</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4621,19 +4621,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E16" t="n">
-        <v>-30.02922713564716</v>
+        <v>-30.02922713564882</v>
       </c>
       <c r="F16" t="n">
-        <v>-7507.306783911789</v>
+        <v>-7507.306783912204</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005111801563984705</v>
+        <v>0.005111801563984978</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.006399919298218829</v>
+        <v>-0.006399919298219385</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00702966564617685</v>
+        <v>0.007029665646177609</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.00793200500685427</v>
+        <v>-0.007932005006854951</v>
       </c>
       <c r="O16" t="n">
-        <v>0.00856876992556288</v>
+        <v>0.008568769925563794</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.002027659871339357</v>
+        <v>-0.00202765987133946</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.009287828678809317</v>
+        <v>-0.009287828678810253</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.005111801563984705</v>
+        <v>-0.005111801563984978</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4681,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.002584932876099717</v>
+        <v>-0.002584932876099851</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.01138677493814868</v>
+        <v>-0.01138677493814981</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.01328450845510865</v>
+        <v>-0.0132845084551094</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>30.02922713564715</v>
+        <v>30.02922713564882</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-30.02922713564715</v>
+        <v>-30.02922713564882</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4749,19 +4749,19 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.869147760388197e-13</v>
+        <v>-8.904913843347609e-13</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.467286940097049e-10</v>
+        <v>-2.226228460836902e-10</v>
       </c>
       <c r="G17" t="n">
-        <v>0.015656775540507</v>
+        <v>0.01565677554050815</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="I17" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.00793200500685427</v>
+        <v>-0.007932005006854951</v>
       </c>
       <c r="O17" t="n">
-        <v>0.00856876992556288</v>
+        <v>0.008568769925563794</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.003454769931294426</v>
+        <v>0.003454769931294883</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.008730048425974309</v>
+        <v>-0.008730048425975126</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.015656775540507</v>
+        <v>-0.01565677554050815</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.003454769931294413</v>
+        <v>0.003454769931294864</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.0111537028016626</v>
+        <v>-0.01115370280166365</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.01328450845510865</v>
+        <v>-0.0132845084551094</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>5.968558980384842e-13</v>
+        <v>8.810729923425242e-13</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-5.968558980384842e-13</v>
+        <v>-8.810729923425242e-13</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4877,19 +4877,19 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>-157.658395118396</v>
+        <v>-157.658395118412</v>
       </c>
       <c r="F18" t="n">
-        <v>-39414.59877959901</v>
+        <v>-39414.598779603</v>
       </c>
       <c r="G18" t="n">
-        <v>0.015656775540507</v>
+        <v>0.01565677554050815</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="I18" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.05054266662275082</v>
+        <v>0.05054266662275473</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="O18" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.015656775540507</v>
+        <v>-0.01565677554050815</v>
       </c>
       <c r="U18" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4937,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.05054266662275082</v>
+        <v>-0.05054266662275473</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>157.6583951183961</v>
+        <v>157.6583951184121</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-157.6583951183961</v>
+        <v>-157.6583951184121</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5011,13 +5011,13 @@
         <v>-6.071532165918825e-11</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.00793200500685427</v>
+        <v>-0.007932005006854951</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00856876992556288</v>
+        <v>0.008568769925563794</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -5029,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.05054266662275082</v>
+        <v>0.05054266662275473</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="O19" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -5047,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.01138677493814868</v>
+        <v>-0.01138677493814982</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.002584932876099718</v>
+        <v>-0.002584932876099851</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.01138677493814869</v>
+        <v>-0.01138677493814982</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.004062312080194719</v>
+        <v>-0.004062312080195014</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.05054266662275082</v>
+        <v>0.05054266662275473</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -5133,19 +5133,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E20" t="n">
-        <v>52.55122238416742</v>
+        <v>52.55122238416967</v>
       </c>
       <c r="F20" t="n">
-        <v>13137.80559604186</v>
+        <v>13137.80559604242</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.00793200500685427</v>
+        <v>-0.007932005006854951</v>
       </c>
       <c r="I20" t="n">
-        <v>0.00856876992556288</v>
+        <v>0.008568769925563794</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.06091050489581464</v>
+        <v>0.06091050489581906</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.007727155750850413</v>
+        <v>-0.007727155750851131</v>
       </c>
       <c r="O20" t="n">
-        <v>0.006973120948370765</v>
+        <v>0.006973120948371539</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0111537028016626</v>
+        <v>-0.01115370280166364</v>
       </c>
       <c r="T20" t="n">
-        <v>0.003454769931294412</v>
+        <v>0.003454769931294863</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.01017847365342086</v>
+        <v>-0.01017847365342187</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.002175322009525313</v>
+        <v>0.002175322009525624</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.06091050489581464</v>
+        <v>0.06091050489581906</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-52.55122238416743</v>
+        <v>-52.55122238416971</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>52.55122238416743</v>
+        <v>52.55122238416971</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>2.833381677428785e-13</v>
+        <v>3.23815048849004e-13</v>
       </c>
       <c r="F21" t="n">
-        <v>7.083454193571961e-11</v>
+        <v>8.095376221225099e-11</v>
       </c>
       <c r="G21" t="n">
-        <v>0.05054266662275082</v>
+        <v>0.05054266662275473</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="I21" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -5285,13 +5285,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.06091050489581464</v>
+        <v>0.06091050489581906</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.007727155750850413</v>
+        <v>-0.007727155750851131</v>
       </c>
       <c r="O21" t="n">
-        <v>0.006973120948370765</v>
+        <v>0.006973120948371539</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.00217532200952531</v>
+        <v>0.002175322009525621</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0118923924037101</v>
+        <v>-0.01189239240371123</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.05054266662275082</v>
+        <v>-0.05054266662275473</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.002175322009525313</v>
+        <v>0.002175322009525625</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.01017847365342086</v>
+        <v>-0.01017847365342187</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.06091050489581464</v>
+        <v>-0.06091050489581906</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-2.842170943040401e-13</v>
+        <v>-3.126388037344441e-13</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.842170943040401e-13</v>
+        <v>3.126388037344441e-13</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5389,19 +5389,19 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>-65.10272033181487</v>
+        <v>-65.10272033182481</v>
       </c>
       <c r="F22" t="n">
-        <v>-16275.68008295372</v>
+        <v>-16275.6800829562</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05054266662275082</v>
+        <v>0.05054266662275473</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="I22" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5413,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.09737080707456244</v>
+        <v>0.09737080707457024</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.01060651122144798</v>
+        <v>-0.01060651122144902</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.05054266662275082</v>
+        <v>-0.05054266662275473</v>
       </c>
       <c r="U22" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5449,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.01060651122144798</v>
+        <v>-0.01060651122144902</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.09737080707456244</v>
+        <v>-0.09737080707457024</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>65.10272033181491</v>
+        <v>65.10272033182486</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>-65.10272033181491</v>
+        <v>-65.10272033182486</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5517,19 +5517,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E23" t="n">
-        <v>53.50696334835187</v>
+        <v>53.50696334835786</v>
       </c>
       <c r="F23" t="n">
-        <v>13376.74083708797</v>
+        <v>13376.74083708946</v>
       </c>
       <c r="G23" t="n">
-        <v>0.06091050489581464</v>
+        <v>0.06091050489581906</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.007727155750850413</v>
+        <v>-0.007727155750851131</v>
       </c>
       <c r="I23" t="n">
-        <v>0.006973120948370765</v>
+        <v>0.006973120948371539</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09737080707456244</v>
+        <v>0.09737080707457024</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.01060651122144798</v>
+        <v>-0.01060651122144902</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -5559,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.01017847365342086</v>
+        <v>-0.01017847365342187</v>
       </c>
       <c r="T23" t="n">
-        <v>0.002175322009525313</v>
+        <v>0.002175322009525624</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06091050489581464</v>
+        <v>0.06091050489581906</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.009185508163298668</v>
+        <v>-0.009185508163299563</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.005303255610723991</v>
+        <v>-0.005303255610724508</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.09737080707456244</v>
+        <v>0.09737080707457024</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>-53.50696334835186</v>
+        <v>-53.50696334835783</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>53.50696334835186</v>
+        <v>53.50696334835783</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5645,10 +5645,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>48.02180217783349</v>
+        <v>48.02180217783598</v>
       </c>
       <c r="F24" t="n">
-        <v>12005.45054445837</v>
+        <v>12005.45054445899</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.000514519309048216</v>
+        <v>0.0005145193090482427</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.000514519309048216</v>
+        <v>0.0005145193090482427</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>-48.02180217783351</v>
+        <v>-48.02180217783599</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>48.02180217783351</v>
+        <v>48.02180217783599</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>8.416897434142326</v>
+        <v>8.416897434142406</v>
       </c>
       <c r="F25" t="n">
-        <v>2104.224358535581</v>
+        <v>2104.224358535601</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005021620520047466</v>
+        <v>0.005021620520047738</v>
       </c>
       <c r="H25" t="n">
-        <v>0.008381677031599073</v>
+        <v>0.008381677031599621</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.01186215091270229</v>
+        <v>-0.01186215091270305</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.005111801563984705</v>
+        <v>0.005111801563984978</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.006399919298218829</v>
+        <v>-0.006399919298219385</v>
       </c>
       <c r="O25" t="n">
-        <v>0.00702966564617685</v>
+        <v>0.007029665646177609</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -5815,13 +5815,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.005021620520047466</v>
+        <v>0.005021620520047738</v>
       </c>
       <c r="T25" t="n">
-        <v>0.008381677031599073</v>
+        <v>0.008381677031599621</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.01186215091270229</v>
+        <v>-0.01186215091270305</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5833,13 +5833,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.005111801563984705</v>
+        <v>0.005111801563984978</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.006399919298218829</v>
+        <v>-0.006399919298219385</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.00702966564617685</v>
+        <v>0.007029665646177609</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>-8.416897434142356</v>
+        <v>-8.416897434142413</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>8.416897434142356</v>
+        <v>8.416897434142413</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5907,13 +5907,13 @@
         <v>-2338.104336630532</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01575698001207688</v>
+        <v>0.01575698001207803</v>
       </c>
       <c r="H26" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -5925,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.015656775540507</v>
+        <v>0.01565677554050815</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="O26" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.01575698001207688</v>
+        <v>0.01575698001207803</v>
       </c>
       <c r="T26" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.015656775540507</v>
+        <v>0.01565677554050815</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -6029,19 +6029,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>13.00308001941958</v>
+        <v>13.00308001941974</v>
       </c>
       <c r="F27" t="n">
-        <v>3250.770004854895</v>
+        <v>3250.770004854935</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01037637654107239</v>
+        <v>0.01037637654107306</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.01543191053294733</v>
+        <v>-0.01543191053294826</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -6053,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.00793200500685427</v>
+        <v>-0.007932005006854951</v>
       </c>
       <c r="O27" t="n">
-        <v>0.00856876992556288</v>
+        <v>0.008568769925563794</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="T27" t="n">
-        <v>0.01037637654107239</v>
+        <v>0.01037637654107306</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.01543191053294733</v>
+        <v>-0.01543191053294826</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.00793200500685427</v>
+        <v>-0.007932005006854951</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.00856876992556288</v>
+        <v>0.008568769925563794</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -6163,13 +6163,13 @@
         <v>-4240.510511622798</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="H28" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -6181,13 +6181,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.05054266662275082</v>
+        <v>0.05054266662275473</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="O28" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -6199,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -6217,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.05054266662275082</v>
+        <v>0.05054266662275473</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -6285,19 +6285,19 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>72.39569072518576</v>
+        <v>72.39569072518705</v>
       </c>
       <c r="F29" t="n">
-        <v>18098.92268129644</v>
+        <v>18098.92268129676</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06013483678090194</v>
+        <v>0.06013483678090634</v>
       </c>
       <c r="H29" t="n">
-        <v>0.006930127646340921</v>
+        <v>0.006930127646341633</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01678443355793183</v>
+        <v>-0.01678443355793261</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -6309,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.06091050489581464</v>
+        <v>0.06091050489581906</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.007727155750850413</v>
+        <v>-0.007727155750851131</v>
       </c>
       <c r="O29" t="n">
-        <v>0.006973120948370765</v>
+        <v>0.006973120948371539</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.06013483678090194</v>
+        <v>0.06013483678090634</v>
       </c>
       <c r="T29" t="n">
-        <v>0.006930127646340921</v>
+        <v>0.006930127646341633</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.01678443355793183</v>
+        <v>-0.01678443355793261</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.06091050489581464</v>
+        <v>0.06091050489581906</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.007727155750850413</v>
+        <v>-0.007727155750851131</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.006973120948370765</v>
+        <v>0.006973120948371539</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>-72.39569072518589</v>
+        <v>-72.39569072518771</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>72.39569072518589</v>
+        <v>72.39569072518771</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6419,10 +6419,10 @@
         <v>282.9104218675845</v>
       </c>
       <c r="G30" t="n">
-        <v>0.09735868234219669</v>
+        <v>0.09735868234220449</v>
       </c>
       <c r="H30" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -6437,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.09737080707456244</v>
+        <v>0.09737080707457024</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.01060651122144798</v>
+        <v>-0.01060651122144902</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -6455,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.09735868234219669</v>
+        <v>0.09735868234220449</v>
       </c>
       <c r="T30" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -6473,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.09737080707456244</v>
+        <v>0.09737080707457024</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.01060651122144798</v>
+        <v>-0.01060651122144902</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>37.32847174831524</v>
+        <v>37.32847174831738</v>
       </c>
       <c r="F31" t="n">
-        <v>9332.117937078809</v>
+        <v>9332.117937079345</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.005111801563984705</v>
+        <v>0.005111801563984978</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.006399919298218829</v>
+        <v>-0.006399919298219385</v>
       </c>
       <c r="O31" t="n">
-        <v>0.00702966564617685</v>
+        <v>0.007029665646177609</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -6601,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.0007998958231781837</v>
+        <v>0.0007998958231782297</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.01058276510922092</v>
+        <v>-0.01058276510922182</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.001967468084983237</v>
+        <v>0.001967468084983633</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-37.32847174831525</v>
+        <v>-37.3284717483174</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>37.32847174831525</v>
+        <v>37.3284717483174</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>-51.50855960893036</v>
+        <v>-51.50855960893236</v>
       </c>
       <c r="F32" t="n">
-        <v>-12877.13990223259</v>
+        <v>-12877.13990223309</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000514519309048216</v>
+        <v>0.0005145193090482427</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6693,13 +6693,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.005021620520047466</v>
+        <v>0.005021620520047738</v>
       </c>
       <c r="N32" t="n">
-        <v>0.008381677031599073</v>
+        <v>0.008381677031599621</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.01186215091270229</v>
+        <v>-0.01186215091270305</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.000257259654524108</v>
+        <v>-0.0002572596545241213</v>
       </c>
       <c r="T32" t="n">
-        <v>0.000291705029246221</v>
+        <v>0.0002917050292462361</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.0003368319543185468</v>
+        <v>-0.0003368319543185642</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.001361014503286902</v>
+        <v>-0.001361014503286957</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.0142151499572058</v>
+        <v>0.01421514995720669</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.005679520930599311</v>
+        <v>0.005679520930599712</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>51.50855960893038</v>
+        <v>51.50855960893237</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>-51.50855960893038</v>
+        <v>-51.50855960893237</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E33" t="n">
-        <v>74.49228351557475</v>
+        <v>74.49228351557826</v>
       </c>
       <c r="F33" t="n">
-        <v>18623.07087889369</v>
+        <v>18623.07087889457</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.015656775540507</v>
+        <v>0.01565677554050815</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="O33" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -6857,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.001784676532928702</v>
+        <v>0.001784676532928786</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.01661246894205048</v>
+        <v>-0.01661246894205172</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-74.49228351557474</v>
+        <v>-74.49228351557826</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>74.49228351557474</v>
+        <v>74.49228351557826</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6925,13 +6925,13 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E34" t="n">
-        <v>-49.79169371734914</v>
+        <v>-49.7916937173524</v>
       </c>
       <c r="F34" t="n">
-        <v>-12447.92342933728</v>
+        <v>-12447.9234293381</v>
       </c>
       <c r="G34" t="n">
-        <v>0.000514519309048216</v>
+        <v>0.0005145193090482427</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.01575698001207688</v>
+        <v>0.01575698001207803</v>
       </c>
       <c r="N34" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.0002301000301536067</v>
+        <v>-0.0002301000301536187</v>
       </c>
       <c r="T34" t="n">
-        <v>0.0004602000603072135</v>
+        <v>0.0004602000603072373</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.001423003014441198</v>
+        <v>-0.001423003014441288</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.01690533770633408</v>
+        <v>0.01690533770633532</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.01307121057345139</v>
+        <v>0.01307121057345221</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>49.79169371734913</v>
+        <v>49.79169371735239</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-49.79169371734913</v>
+        <v>-49.79169371735239</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7053,19 +7053,19 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>34.67476474064564</v>
+        <v>34.67476474064762</v>
       </c>
       <c r="F35" t="n">
-        <v>8668.69118516141</v>
+        <v>8668.691185161906</v>
       </c>
       <c r="G35" t="n">
-        <v>0.005021620520047466</v>
+        <v>0.005021620520047738</v>
       </c>
       <c r="H35" t="n">
-        <v>0.008381677031599073</v>
+        <v>0.008381677031599621</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.01186215091270229</v>
+        <v>-0.01186215091270305</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -7077,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.00793200500685427</v>
+        <v>-0.007932005006854951</v>
       </c>
       <c r="O35" t="n">
-        <v>0.00856876992556288</v>
+        <v>0.008568769925563794</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.003660606016760564</v>
+        <v>0.003660606016760781</v>
       </c>
       <c r="T35" t="n">
-        <v>0.00852116749666961</v>
+        <v>0.008521167496670194</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.01225436554330246</v>
+        <v>-0.01225436554330322</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7113,13 +7113,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.004403636689774399</v>
+        <v>0.004403636689774658</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.01698531903161294</v>
+        <v>-0.01698531903161427</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.002219371005182661</v>
+        <v>-0.002219371005182461</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>-34.67476474064566</v>
+        <v>-34.67476474064765</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>34.67476474064566</v>
+        <v>34.67476474064765</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7181,19 +7181,19 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>-54.16226661660009</v>
+        <v>-54.1622666166022</v>
       </c>
       <c r="F36" t="n">
-        <v>-13540.56665415002</v>
+        <v>-13540.56665415055</v>
       </c>
       <c r="G36" t="n">
-        <v>0.005111801563984705</v>
+        <v>0.005111801563984978</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.006399919298218829</v>
+        <v>-0.006399919298219385</v>
       </c>
       <c r="I36" t="n">
-        <v>0.00702966564617685</v>
+        <v>0.007029665646177609</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -7205,13 +7205,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="N36" t="n">
-        <v>0.01037637654107239</v>
+        <v>0.01037637654107306</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.01543191053294733</v>
+        <v>-0.01543191053294826</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -7223,13 +7223,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.004311905740806522</v>
+        <v>-0.004311905740806748</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.004786526956443255</v>
+        <v>-0.004786526956443842</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.00866038740056997</v>
+        <v>-0.008660387400570721</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7241,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.005472525739733666</v>
+        <v>-0.005472525739733938</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.02189286768611054</v>
+        <v>0.02189286768611187</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.003059881148375593</v>
+        <v>0.003059881148375805</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>54.16226661660011</v>
+        <v>54.16226661660221</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>-54.16226661660011</v>
+        <v>-54.16226661660221</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7309,19 +7309,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E37" t="n">
-        <v>70.70433465812155</v>
+        <v>70.70433465812481</v>
       </c>
       <c r="F37" t="n">
-        <v>17676.08366453039</v>
+        <v>17676.0836645312</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01575698001207688</v>
+        <v>0.01575698001207803</v>
       </c>
       <c r="H37" t="n">
-        <v>0.006287524269799625</v>
+        <v>0.006287524269800096</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -7333,13 +7333,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.05054266662275082</v>
+        <v>0.05054266662275473</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="O37" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01267046835640255</v>
+        <v>0.01267046835640348</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.01128160503535341</v>
+        <v>-0.01128160503535422</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.01307121057345139</v>
+        <v>-0.01307121057345221</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7369,13 +7369,13 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.01436439369853956</v>
+        <v>0.01436439369854057</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0.0493262223170205</v>
+        <v>-0.04932622231702436</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>-70.70433465812164</v>
+        <v>-70.70433465812482</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>70.70433465812164</v>
+        <v>70.70433465812482</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7437,19 +7437,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E38" t="n">
-        <v>-53.57964257480307</v>
+        <v>-53.57964257480648</v>
       </c>
       <c r="F38" t="n">
-        <v>-13394.91064370077</v>
+        <v>-13394.91064370162</v>
       </c>
       <c r="G38" t="n">
-        <v>0.015656775540507</v>
+        <v>0.01565677554050815</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.005833058747514891</v>
+        <v>-0.005833058747515369</v>
       </c>
       <c r="I38" t="n">
-        <v>0.007356942737718746</v>
+        <v>0.00735694273771955</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -7461,13 +7461,13 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="N38" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>-0.01221916923388316</v>
+        <v>-0.01221916923388411</v>
       </c>
       <c r="T38" t="n">
-        <v>0.01139522259157325</v>
+        <v>0.01139522259157406</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.007356942737718746</v>
+        <v>-0.00735694273771955</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.01350282340896247</v>
+        <v>-0.01350282340896349</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.04996019467102242</v>
+        <v>0.04996019467102628</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.0176387326946877</v>
+        <v>0.01763873269468855</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>53.57964257480313</v>
+        <v>53.57964257480648</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>-53.57964257480313</v>
+        <v>-53.57964257480648</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7565,19 +7565,19 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>28.15610657775992</v>
+        <v>28.15610657776235</v>
       </c>
       <c r="F39" t="n">
-        <v>7039.026644439979</v>
+        <v>7039.026644440587</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01314518974061487</v>
+        <v>0.01314518974061562</v>
       </c>
       <c r="H39" t="n">
-        <v>0.01037637654107239</v>
+        <v>0.01037637654107306</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.01543191053294733</v>
+        <v>-0.01543191053294826</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7589,13 +7589,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.06091050489581464</v>
+        <v>0.06091050489581906</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.007727155750850413</v>
+        <v>-0.007727155750851131</v>
       </c>
       <c r="O39" t="n">
-        <v>0.006973120948370765</v>
+        <v>0.006973120948371539</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.02103709055134225</v>
+        <v>0.02103709055134353</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.008166211767289466</v>
+        <v>-0.008166211767289901</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.003059881148375593</v>
+        <v>-0.003059881148375805</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -7625,13 +7625,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.02164043569229425</v>
+        <v>0.02164043569229558</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.03622030902130579</v>
+        <v>-0.03622030902130839</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.04514646958368239</v>
+        <v>0.04514646958368587</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>-28.15610657775994</v>
+        <v>-28.15610657776233</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>28.15610657775994</v>
+        <v>28.15610657776233</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7693,19 +7693,19 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>-60.68092477948557</v>
+        <v>-60.68092477948768</v>
       </c>
       <c r="F40" t="n">
-        <v>-15170.23119487139</v>
+        <v>-15170.23119487192</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01328450845510865</v>
+        <v>0.0132845084551094</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.00793200500685427</v>
+        <v>-0.007932005006854951</v>
       </c>
       <c r="I40" t="n">
-        <v>0.00856876992556288</v>
+        <v>0.008568769925563794</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7717,13 +7717,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.06013483678090194</v>
+        <v>0.06013483678090634</v>
       </c>
       <c r="N40" t="n">
-        <v>0.006930127646340921</v>
+        <v>0.006930127646341633</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.01678443355793183</v>
+        <v>-0.01678443355793261</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.0163016442000558</v>
+        <v>-0.01630164420005709</v>
       </c>
       <c r="T40" t="n">
-        <v>0.006492262708485148</v>
+        <v>0.006492262708485571</v>
       </c>
       <c r="U40" t="n">
-        <v>0.002219371005182661</v>
+        <v>0.002219371005182461</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.01760194973104478</v>
+        <v>-0.01760194973104611</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.03043610313703144</v>
+        <v>0.03043610313703402</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.05205533080500672</v>
+        <v>0.05205533080501019</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>60.68092477948562</v>
+        <v>60.68092477948767</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>-60.68092477948562</v>
+        <v>-60.68092477948767</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7821,19 +7821,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E41" t="n">
-        <v>91.50792162796985</v>
+        <v>91.50792162797391</v>
       </c>
       <c r="F41" t="n">
-        <v>22876.98040699246</v>
+        <v>22876.98040699348</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05072440278753466</v>
+        <v>0.05072440278753856</v>
       </c>
       <c r="H41" t="n">
-        <v>0.01026558587845957</v>
+        <v>0.01026558587846038</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.09737080707456244</v>
+        <v>0.09737080707457024</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.01060651122144798</v>
+        <v>-0.01060651122144902</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.03186646169144046</v>
+        <v>0.03186646169144293</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.04077837552978342</v>
+        <v>-0.04077837552978656</v>
       </c>
       <c r="U41" t="n">
-        <v>-0.0176387326946877</v>
+        <v>-0.01763873269468855</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.034058796690439</v>
+        <v>0.03405879669044157</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.09183447347615002</v>
+        <v>-0.09183447347615746</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-91.50792162796984</v>
+        <v>-91.50792162797393</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>91.50792162796984</v>
+        <v>91.50792162797393</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7949,19 +7949,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E42" t="n">
-        <v>-32.77605560495774</v>
+        <v>-32.7760556049618</v>
       </c>
       <c r="F42" t="n">
-        <v>-8194.013901239436</v>
+        <v>-8194.013901240449</v>
       </c>
       <c r="G42" t="n">
-        <v>0.05054266662275082</v>
+        <v>0.05054266662275473</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.009211452928623378</v>
+        <v>-0.009211452928624199</v>
       </c>
       <c r="I42" t="n">
-        <v>0.007830080323515384</v>
+        <v>0.007830080323516217</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.09735868234219669</v>
+        <v>0.09735868234220449</v>
       </c>
       <c r="N42" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.03084234163449267</v>
+        <v>-0.03084234163449515</v>
       </c>
       <c r="T42" t="n">
-        <v>0.04108724834904395</v>
+        <v>0.04108724834904707</v>
       </c>
       <c r="U42" t="n">
-        <v>-0.007830080323515384</v>
+        <v>-0.007830080323516217</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.03162758615271051</v>
+        <v>-0.03162758615271308</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.09303652288212486</v>
+        <v>0.09303652288213229</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>32.77605560495772</v>
+        <v>32.77605560496181</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>-32.77605560495772</v>
+        <v>-32.77605560496181</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8077,19 +8077,19 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>-84.11045667088982</v>
+        <v>-84.11045667088723</v>
       </c>
       <c r="F43" t="n">
-        <v>-21027.61416772246</v>
+        <v>-21027.61416772181</v>
       </c>
       <c r="G43" t="n">
-        <v>0.06013483678090194</v>
+        <v>0.06013483678090634</v>
       </c>
       <c r="H43" t="n">
-        <v>0.006930127646340921</v>
+        <v>0.006930127646341633</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.01678443355793183</v>
+        <v>-0.01678443355793261</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -8101,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.09737080707456244</v>
+        <v>0.09737080707457024</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.01060651122144798</v>
+        <v>-0.01060651122144902</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -8119,13 +8119,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.04253288704985716</v>
+        <v>0.04253288704986023</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.03775039254313705</v>
+        <v>-0.03775039254313946</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02667965246707835</v>
+        <v>0.02667965246708064</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.04073052012119523</v>
+        <v>0.04073052012119836</v>
       </c>
       <c r="Z43" t="n">
-        <v>-0.06221960641612202</v>
+        <v>-0.06221960641612712</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.06374415627116058</v>
+        <v>0.06374415627116568</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>84.11045667089002</v>
+        <v>84.11045667088729</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>-84.11045667089002</v>
+        <v>-84.11045667088729</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8205,19 +8205,19 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>27.05251197186513</v>
+        <v>27.05251197186319</v>
       </c>
       <c r="F44" t="n">
-        <v>6763.127992966283</v>
+        <v>6763.127992965799</v>
       </c>
       <c r="G44" t="n">
-        <v>0.06091050489581464</v>
+        <v>0.06091050489581906</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.007727155750850413</v>
+        <v>-0.007727155750851131</v>
       </c>
       <c r="I44" t="n">
-        <v>0.006973120948370765</v>
+        <v>0.006973120948371539</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.09735868234219669</v>
+        <v>0.09735868234220449</v>
       </c>
       <c r="N44" t="n">
-        <v>0.01331862487025247</v>
+        <v>0.0133186248702535</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -8247,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.03927006920352039</v>
+        <v>-0.03927006920352347</v>
       </c>
       <c r="T44" t="n">
-        <v>0.03284571162971182</v>
+        <v>0.03284571162971422</v>
       </c>
       <c r="U44" t="n">
-        <v>0.03460410164576015</v>
+        <v>0.03460410164576246</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8265,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>-0.03869037251840899</v>
+        <v>-0.03869037251841212</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.06400662689952367</v>
+        <v>0.06400662689952878</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.06373621877061099</v>
+        <v>0.0637362187706161</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>-27.05251197186521</v>
+        <v>-27.05251197186317</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>27.05251197186521</v>
+        <v>27.05251197186317</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>

--- a/outputs/validation_truss_nodal_loads.xlsx
+++ b/outputs/validation_truss_nodal_loads.xlsx
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005145193090482427</v>
+        <v>0.000514519309048216</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005145193090482427</v>
+        <v>0.000514519309048216</v>
       </c>
     </row>
     <row r="4">
@@ -573,13 +573,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005021620520047738</v>
+        <v>0.005021620520047466</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008381677031599621</v>
+        <v>0.008381677031599073</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.01186215091270305</v>
+        <v>-0.01186215091270229</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01536814259385795</v>
+        <v>0.01536814259385697</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005111801563984978</v>
+        <v>0.005111801563984705</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.006399919298219385</v>
+        <v>-0.006399919298218829</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007029665646177609</v>
+        <v>0.00702966564617685</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01079377975272471</v>
+        <v>0.01079377975272375</v>
       </c>
     </row>
     <row r="6">
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01575698001207803</v>
+        <v>0.01575698001207688</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02141662733485085</v>
+        <v>0.02141662733484937</v>
       </c>
     </row>
     <row r="7">
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01565677554050815</v>
+        <v>0.015656775540507</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01825606203768776</v>
+        <v>0.0182560620376863</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01037637654107306</v>
+        <v>0.01037637654107239</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01543191053294826</v>
+        <v>-0.01543191053294733</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02277298983743323</v>
+        <v>0.02277298983743186</v>
       </c>
     </row>
     <row r="9">
@@ -748,13 +748,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.007932005006854951</v>
+        <v>-0.00793200500685427</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008568769925563794</v>
+        <v>0.00856876992556288</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01768668104421776</v>
+        <v>0.01768668104421645</v>
       </c>
     </row>
     <row r="10">
@@ -783,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.05467606590323749</v>
+        <v>0.05467606590323344</v>
       </c>
     </row>
     <row r="11">
@@ -818,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05054266662275473</v>
+        <v>0.05054266662275082</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="G11" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0519684728683449</v>
+        <v>0.05196847286834083</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06013483678090634</v>
+        <v>0.06013483678090194</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006930127646341633</v>
+        <v>0.006930127646340921</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01678443355793261</v>
+        <v>-0.01678443355793183</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06281673721008986</v>
+        <v>0.06281673721008536</v>
       </c>
     </row>
     <row r="13">
@@ -888,13 +888,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06091050489581906</v>
+        <v>0.06091050489581464</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.007727155750851131</v>
+        <v>-0.007727155750850413</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006973120948371539</v>
+        <v>0.006973120948370765</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06179338927767376</v>
+        <v>0.06179338927766923</v>
       </c>
     </row>
     <row r="14">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09735868234220449</v>
+        <v>0.09735868234219669</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09826545067237424</v>
+        <v>0.09826545067236638</v>
       </c>
     </row>
     <row r="15">
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09737080707457024</v>
+        <v>0.09737080707456244</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01060651122144902</v>
+        <v>-0.01060651122144798</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09794678223731448</v>
+        <v>0.09794678223730661</v>
       </c>
     </row>
   </sheetData>
@@ -1035,13 +1035,13 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09826545067237424</v>
+        <v>0.09826545067236638</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09735868234220449</v>
+        <v>0.09735868234219669</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1057,13 +1057,13 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09737080707457024</v>
+        <v>0.09737080707456244</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09737080707457024</v>
+        <v>0.09737080707456244</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01060651122144902</v>
+        <v>-0.01060651122144798</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1079,13 +1079,13 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09735868234220449</v>
+        <v>0.09735868234219669</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1101,16 +1101,16 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
     </row>
   </sheetData>
@@ -1154,13 +1154,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-99.99999999999871</v>
+        <v>-99.99999999999355</v>
       </c>
       <c r="C2" t="n">
-        <v>-449.9999999999975</v>
+        <v>-449.9999999999666</v>
       </c>
       <c r="D2" t="n">
-        <v>-51.93512595217241</v>
+        <v>-51.93512595216902</v>
       </c>
     </row>
     <row r="3">
@@ -1169,10 +1169,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>449.9999999999976</v>
+        <v>449.9999999999662</v>
       </c>
       <c r="D3" t="n">
-        <v>76.93512595217273</v>
+        <v>76.93512595216902</v>
       </c>
     </row>
     <row r="4">
@@ -1182,7 +1182,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>65.33258557373006</v>
+        <v>65.33258557372574</v>
       </c>
     </row>
     <row r="5">
@@ -1192,7 +1192,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>9.667414426270284</v>
+        <v>9.66741442627449</v>
       </c>
     </row>
   </sheetData>
@@ -1275,16 +1275,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001047920711633349</v>
+        <v>0.001047920711633271</v>
       </c>
       <c r="H2" t="n">
-        <v>293.4177992573378</v>
+        <v>293.4177992573158</v>
       </c>
       <c r="I2" t="n">
-        <v>73354.44981433444</v>
+        <v>73354.44981432894</v>
       </c>
     </row>
     <row r="3">
@@ -1306,16 +1306,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00132766977933029</v>
+        <v>0.001327669779330199</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002555101681637581</v>
+        <v>0.0002555101681637406</v>
       </c>
       <c r="H3" t="n">
-        <v>71.54284708585226</v>
+        <v>71.54284708584736</v>
       </c>
       <c r="I3" t="n">
-        <v>17885.71177146307</v>
+        <v>17885.71177146184</v>
       </c>
     </row>
     <row r="4">
@@ -1337,16 +1337,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.734723475976807e-18</v>
+        <v>-3.469446951953614e-18</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.782411586589357e-19</v>
+        <v>-1.156482317317871e-18</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.61907524424502e-13</v>
+        <v>-3.23815048849004e-13</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.04768811061255e-11</v>
+        <v>-8.095376221225099e-11</v>
       </c>
     </row>
     <row r="5">
@@ -1368,16 +1368,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.741936200224455e-05</v>
+        <v>-5.74193620022723e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.105036136956415e-05</v>
+        <v>-1.105036136956949e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.094101183477963</v>
+        <v>-3.094101183479459</v>
       </c>
       <c r="I5" t="n">
-        <v>-773.5252958694907</v>
+        <v>-773.5252958698646</v>
       </c>
     </row>
     <row r="6">
@@ -1399,16 +1399,16 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>1.734723475976807e-18</v>
       </c>
       <c r="G6" t="n">
-        <v>5.782411586589357e-19</v>
+        <v>2.891205793294678e-19</v>
       </c>
       <c r="H6" t="n">
-        <v>1.61907524424502e-13</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="I6" t="n">
-        <v>4.04768811061255e-11</v>
+        <v>2.023844055306275e-11</v>
       </c>
     </row>
     <row r="7">
@@ -1430,16 +1430,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003978061608660286</v>
+        <v>0.003978061608659943</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0006630102681100476</v>
+        <v>0.0006630102681099906</v>
       </c>
       <c r="H7" t="n">
-        <v>185.6428750708133</v>
+        <v>185.6428750707973</v>
       </c>
       <c r="I7" t="n">
-        <v>46410.71876770334</v>
+        <v>46410.71876769933</v>
       </c>
     </row>
     <row r="8">
@@ -1461,16 +1461,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001855768722395242</v>
+        <v>0.001855768722395238</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003092947870658736</v>
+        <v>0.000309294787065873</v>
       </c>
       <c r="H8" t="n">
-        <v>86.6025403784446</v>
+        <v>86.60254037844444</v>
       </c>
       <c r="I8" t="n">
-        <v>21650.63509461115</v>
+        <v>21650.63509461111</v>
       </c>
     </row>
     <row r="9">
@@ -1492,16 +1492,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.002308277578109291</v>
+        <v>-0.002308277578109251</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0004442282270285921</v>
+        <v>-0.0004442282270285844</v>
       </c>
       <c r="H9" t="n">
-        <v>-124.3839035680058</v>
+        <v>-124.3839035680036</v>
       </c>
       <c r="I9" t="n">
-        <v>-31095.97589200145</v>
+        <v>-31095.97589200091</v>
       </c>
     </row>
     <row r="10">
@@ -1523,16 +1523,16 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0009278843611976138</v>
+        <v>-0.0009278843611976173</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0003092947870658713</v>
+        <v>-0.0003092947870658724</v>
       </c>
       <c r="H10" t="n">
-        <v>-86.60254037844395</v>
+        <v>-86.60254037844427</v>
       </c>
       <c r="I10" t="n">
-        <v>-21650.63509461099</v>
+        <v>-21650.63509461107</v>
       </c>
     </row>
     <row r="11">
@@ -1554,16 +1554,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003053038991793114</v>
+        <v>0.003053038991792902</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000508839831965519</v>
+        <v>0.0005088398319654837</v>
       </c>
       <c r="H11" t="n">
-        <v>142.4751529503453</v>
+        <v>142.4751529503354</v>
       </c>
       <c r="I11" t="n">
-        <v>35618.78823758633</v>
+        <v>35618.78823758385</v>
       </c>
     </row>
     <row r="12">
@@ -1585,16 +1585,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.00285961589105227</v>
+        <v>-0.00285961589105215</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0005503333348259865</v>
+        <v>-0.0005503333348259634</v>
       </c>
       <c r="H12" t="n">
-        <v>-154.0933337512762</v>
+        <v>-154.0933337512698</v>
       </c>
       <c r="I12" t="n">
-        <v>-38523.33343781906</v>
+        <v>-38523.33343781744</v>
       </c>
     </row>
     <row r="13">
@@ -1616,16 +1616,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009721764579192282</v>
+        <v>-0.0009721764579191486</v>
       </c>
       <c r="H13" t="n">
-        <v>-272.2094082173839</v>
+        <v>-272.2094082173616</v>
       </c>
       <c r="I13" t="n">
-        <v>-68052.35205434597</v>
+        <v>-68052.3520543404</v>
       </c>
     </row>
     <row r="14">
@@ -1647,16 +1647,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.00202765987133946</v>
+        <v>-0.002027659871339357</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0003902233241809464</v>
+        <v>-0.0003902233241809266</v>
       </c>
       <c r="H14" t="n">
-        <v>-109.262530770665</v>
+        <v>-109.2625307706595</v>
       </c>
       <c r="I14" t="n">
-        <v>-27315.63269266625</v>
+        <v>-27315.63269266486</v>
       </c>
     </row>
     <row r="15">
@@ -1678,16 +1678,16 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.734723475976807e-18</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>5.782411586589357e-19</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1.61907524424502e-13</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>4.04768811061255e-11</v>
       </c>
     </row>
     <row r="16">
@@ -1709,16 +1709,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0005572730047603905</v>
+        <v>-0.0005572730047603597</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0001072472397701743</v>
+        <v>-0.0001072472397701684</v>
       </c>
       <c r="H16" t="n">
-        <v>-30.02922713564882</v>
+        <v>-30.02922713564716</v>
       </c>
       <c r="I16" t="n">
-        <v>-7507.306783912204</v>
+        <v>-7507.306783911789</v>
       </c>
     </row>
     <row r="17">
@@ -1740,16 +1740,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.908195823574488e-17</v>
+        <v>-1.257674520083185e-17</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.180326372624146e-18</v>
+        <v>-2.096124200138642e-18</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.904913843347609e-13</v>
+        <v>-5.869147760388197e-13</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.226228460836902e-10</v>
+        <v>-1.467286940097049e-10</v>
       </c>
     </row>
     <row r="18">
@@ -1771,16 +1771,16 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.003378394181108829</v>
+        <v>-0.003378394181108487</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0005630656968514716</v>
+        <v>-0.0005630656968514144</v>
       </c>
       <c r="H18" t="n">
-        <v>-157.658395118412</v>
+        <v>-157.658395118396</v>
       </c>
       <c r="I18" t="n">
-        <v>-39414.598779603</v>
+        <v>-39414.59877959901</v>
       </c>
     </row>
     <row r="19">
@@ -1833,16 +1833,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0009752291482417793</v>
+        <v>0.0009752291482417377</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0001876829370863202</v>
+        <v>0.0001876829370863122</v>
       </c>
       <c r="H20" t="n">
-        <v>52.55122238416967</v>
+        <v>52.55122238416742</v>
       </c>
       <c r="I20" t="n">
-        <v>13137.80559604242</v>
+        <v>13137.80559604186</v>
       </c>
     </row>
     <row r="21">
@@ -1864,16 +1864,16 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>3.035766082959412e-18</v>
       </c>
       <c r="G21" t="n">
-        <v>1.156482317317871e-18</v>
+        <v>1.011922027653138e-18</v>
       </c>
       <c r="H21" t="n">
-        <v>3.23815048849004e-13</v>
+        <v>2.833381677428785e-13</v>
       </c>
       <c r="I21" t="n">
-        <v>8.095376221225099e-11</v>
+        <v>7.083454193571961e-11</v>
       </c>
     </row>
     <row r="22">
@@ -1895,16 +1895,16 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.001395058292824818</v>
+        <v>-0.001395058292824604</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0002325097154708029</v>
+        <v>-0.0002325097154707674</v>
       </c>
       <c r="H22" t="n">
-        <v>-65.10272033182481</v>
+        <v>-65.10272033181487</v>
       </c>
       <c r="I22" t="n">
-        <v>-16275.6800829562</v>
+        <v>-16275.68008295372</v>
       </c>
     </row>
     <row r="23">
@@ -1926,16 +1926,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0009929654901223023</v>
+        <v>0.0009929654901221913</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001910962976727066</v>
+        <v>0.0001910962976726853</v>
       </c>
       <c r="H23" t="n">
-        <v>53.50696334835786</v>
+        <v>53.50696334835187</v>
       </c>
       <c r="I23" t="n">
-        <v>13376.74083708946</v>
+        <v>13376.74083708797</v>
       </c>
     </row>
     <row r="24">
@@ -1957,16 +1957,16 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0005145193090482427</v>
+        <v>0.000514519309048216</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0001715064363494142</v>
+        <v>0.0001715064363494053</v>
       </c>
       <c r="H24" t="n">
-        <v>48.02180217783598</v>
+        <v>48.02180217783349</v>
       </c>
       <c r="I24" t="n">
-        <v>12005.45054445899</v>
+        <v>12005.45054445837</v>
       </c>
     </row>
     <row r="25">
@@ -1988,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>9.018104393724007e-05</v>
+        <v>9.018104393723921e-05</v>
       </c>
       <c r="G25" t="n">
-        <v>3.006034797908002e-05</v>
+        <v>3.006034797907974e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>8.416897434142406</v>
+        <v>8.416897434142326</v>
       </c>
       <c r="I25" t="n">
-        <v>2104.224358535601</v>
+        <v>2104.224358535581</v>
       </c>
     </row>
     <row r="26">
@@ -2050,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>0.000139318714493783</v>
+        <v>0.0001393187144937812</v>
       </c>
       <c r="G27" t="n">
-        <v>4.643957149792766e-05</v>
+        <v>4.643957149792708e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>13.00308001941974</v>
+        <v>13.00308001941958</v>
       </c>
       <c r="I27" t="n">
-        <v>3250.770004854935</v>
+        <v>3250.770004854895</v>
       </c>
     </row>
     <row r="28">
@@ -2112,16 +2112,16 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0007756681149127184</v>
+        <v>0.0007756681149127045</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0002585560383042395</v>
+        <v>0.0002585560383042348</v>
       </c>
       <c r="H29" t="n">
-        <v>72.39569072518705</v>
+        <v>72.39569072518576</v>
       </c>
       <c r="I29" t="n">
-        <v>18098.92268129676</v>
+        <v>18098.92268129644</v>
       </c>
     </row>
     <row r="30">
@@ -2174,16 +2174,16 @@
         <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0007998958231782297</v>
+        <v>0.0007998958231781837</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0001333159705297049</v>
+        <v>0.0001333159705296973</v>
       </c>
       <c r="H31" t="n">
-        <v>37.32847174831738</v>
+        <v>37.32847174831524</v>
       </c>
       <c r="I31" t="n">
-        <v>9332.117937079345</v>
+        <v>9332.117937078809</v>
       </c>
     </row>
     <row r="32">
@@ -2205,16 +2205,16 @@
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.001103754848762836</v>
+        <v>-0.001103754848762794</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0001839591414604727</v>
+        <v>-0.0001839591414604656</v>
       </c>
       <c r="H32" t="n">
-        <v>-51.50855960893236</v>
+        <v>-51.50855960893036</v>
       </c>
       <c r="I32" t="n">
-        <v>-12877.13990223309</v>
+        <v>-12877.13990223259</v>
       </c>
     </row>
     <row r="33">
@@ -2236,16 +2236,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F33" t="n">
-        <v>0.001784676532928786</v>
+        <v>0.001784676532928702</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0002660438696984938</v>
+        <v>0.0002660438696984812</v>
       </c>
       <c r="H33" t="n">
-        <v>74.49228351557826</v>
+        <v>74.49228351557475</v>
       </c>
       <c r="I33" t="n">
-        <v>18623.07087889457</v>
+        <v>18623.07087889369</v>
       </c>
     </row>
     <row r="34">
@@ -2267,16 +2267,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.00119290298428767</v>
+        <v>-0.001192902984287592</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0001778274775619729</v>
+        <v>-0.0001778274775619612</v>
       </c>
       <c r="H34" t="n">
-        <v>-49.7916937173524</v>
+        <v>-49.79169371734914</v>
       </c>
       <c r="I34" t="n">
-        <v>-12447.9234293381</v>
+        <v>-12447.92342933728</v>
       </c>
     </row>
     <row r="35">
@@ -2298,16 +2298,16 @@
         <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0007430306730138777</v>
+        <v>0.0007430306730138352</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0001238384455023129</v>
+        <v>0.0001238384455023059</v>
       </c>
       <c r="H35" t="n">
-        <v>34.67476474064762</v>
+        <v>34.67476474064564</v>
       </c>
       <c r="I35" t="n">
-        <v>8668.691185161906</v>
+        <v>8668.69118516141</v>
       </c>
     </row>
     <row r="36">
@@ -2329,16 +2329,16 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.00116061999892719</v>
+        <v>-0.001160619998927145</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.000193436666487865</v>
+        <v>-0.0001934366664878575</v>
       </c>
       <c r="H36" t="n">
-        <v>-54.1622666166022</v>
+        <v>-54.16226661660009</v>
       </c>
       <c r="I36" t="n">
-        <v>-13540.56665415055</v>
+        <v>-13540.56665415002</v>
       </c>
     </row>
     <row r="37">
@@ -2360,16 +2360,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F37" t="n">
-        <v>0.001693925342137087</v>
+        <v>0.001693925342137009</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0002525154809218743</v>
+        <v>0.0002525154809218626</v>
       </c>
       <c r="H37" t="n">
-        <v>70.70433465812481</v>
+        <v>70.70433465812155</v>
       </c>
       <c r="I37" t="n">
-        <v>17676.0836645312</v>
+        <v>17676.08366453039</v>
       </c>
     </row>
     <row r="38">
@@ -2391,16 +2391,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.001283654175079384</v>
+        <v>-0.001283654175079302</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0001913558663385945</v>
+        <v>-0.0001913558663385824</v>
       </c>
       <c r="H38" t="n">
-        <v>-53.57964257480648</v>
+        <v>-53.57964257480307</v>
       </c>
       <c r="I38" t="n">
-        <v>-13394.91064370162</v>
+        <v>-13394.91064370077</v>
       </c>
     </row>
     <row r="39">
@@ -2422,16 +2422,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0006033451409520503</v>
+        <v>0.0006033451409519983</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0001005575234920084</v>
+        <v>0.0001005575234919997</v>
       </c>
       <c r="H39" t="n">
-        <v>28.15610657776235</v>
+        <v>28.15610657775992</v>
       </c>
       <c r="I39" t="n">
-        <v>7039.026644440587</v>
+        <v>7039.026644439979</v>
       </c>
     </row>
     <row r="40">
@@ -2453,16 +2453,16 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.001300305530989022</v>
+        <v>-0.001300305530988977</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0002167175884981703</v>
+        <v>-0.0002167175884981628</v>
       </c>
       <c r="H40" t="n">
-        <v>-60.68092477948768</v>
+        <v>-60.68092477948557</v>
       </c>
       <c r="I40" t="n">
-        <v>-15170.23119487192</v>
+        <v>-15170.23119487139</v>
       </c>
     </row>
     <row r="41">
@@ -2484,16 +2484,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F41" t="n">
-        <v>0.002192334998998638</v>
+        <v>0.002192334998998541</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0003268140058141925</v>
+        <v>0.000326814005814178</v>
       </c>
       <c r="H41" t="n">
-        <v>91.50792162797391</v>
+        <v>91.50792162796985</v>
       </c>
       <c r="I41" t="n">
-        <v>22876.98040699348</v>
+        <v>22876.98040699246</v>
       </c>
     </row>
     <row r="42">
@@ -2515,16 +2515,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.0007852445182179382</v>
+        <v>-0.0007852445182178411</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.0001170573414462921</v>
+        <v>-0.0001170573414462776</v>
       </c>
       <c r="H42" t="n">
-        <v>-32.7760556049618</v>
+        <v>-32.77605560495774</v>
       </c>
       <c r="I42" t="n">
-        <v>-8194.013901240449</v>
+        <v>-8194.013901239436</v>
       </c>
     </row>
     <row r="43">
@@ -2546,16 +2546,16 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.001802366928661869</v>
+        <v>-0.001802366928661925</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.0003003944881103116</v>
+        <v>-0.0003003944881103208</v>
       </c>
       <c r="H43" t="n">
-        <v>-84.11045667088723</v>
+        <v>-84.11045667088982</v>
       </c>
       <c r="I43" t="n">
-        <v>-21027.61416772181</v>
+        <v>-21027.61416772246</v>
       </c>
     </row>
     <row r="44">
@@ -2577,16 +2577,16 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0005796966851113541</v>
+        <v>0.0005796966851113958</v>
       </c>
       <c r="G44" t="n">
-        <v>9.661611418522569e-05</v>
+        <v>9.661611418523262e-05</v>
       </c>
       <c r="H44" t="n">
-        <v>27.05251197186319</v>
+        <v>27.05251197186513</v>
       </c>
       <c r="I44" t="n">
-        <v>6763.127992965799</v>
+        <v>6763.127992966283</v>
       </c>
     </row>
   </sheetData>
@@ -2829,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>293.4177992573378</v>
+        <v>293.4177992573158</v>
       </c>
       <c r="F2" t="n">
-        <v>73354.44981433444</v>
+        <v>73354.44981432894</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01575698001207803</v>
+        <v>0.01575698001207688</v>
       </c>
       <c r="N2" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.01575698001207803</v>
+        <v>-0.01575698001207688</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-293.4177992573379</v>
+        <v>-293.4177992573159</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>293.4177992573379</v>
+        <v>293.4177992573159</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E3" t="n">
-        <v>71.54284708585226</v>
+        <v>71.54284708584736</v>
       </c>
       <c r="F3" t="n">
-        <v>17885.71177146307</v>
+        <v>17885.71177146184</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.005021620520047738</v>
+        <v>0.005021620520047466</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008381677031599621</v>
+        <v>0.008381677031599073</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.01186215091270305</v>
+        <v>-0.01186215091270229</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00132766977933029</v>
+        <v>0.001327669779330199</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01446376254972542</v>
+        <v>0.01446376254972448</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.005021620520047738</v>
+        <v>-0.005021620520047466</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-71.54284708585226</v>
+        <v>-71.54284708584736</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>71.54284708585226</v>
+        <v>71.54284708584736</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.61907524424502e-13</v>
+        <v>-3.23815048849004e-13</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.04768811061255e-11</v>
+        <v>-8.095376221225099e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005021620520047738</v>
+        <v>0.005021620520047466</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008381677031599621</v>
+        <v>0.008381677031599073</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01186215091270305</v>
+        <v>-0.01186215091270229</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01575698001207803</v>
+        <v>0.01575698001207688</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01446376254972542</v>
+        <v>0.01446376254972448</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001327669779330291</v>
+        <v>0.0013276697793302</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005021620520047738</v>
+        <v>0.005021620520047466</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01446376254972542</v>
+        <v>0.01446376254972448</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.001090449542168017</v>
+        <v>-0.001090449542168018</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01575698001207803</v>
+        <v>0.01575698001207688</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.094101183477963</v>
+        <v>-3.094101183479459</v>
       </c>
       <c r="F5" t="n">
-        <v>-773.5252958694907</v>
+        <v>-773.5252958698646</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005021620520047738</v>
+        <v>0.005021620520047466</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008381677031599621</v>
+        <v>0.008381677031599073</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01186215091270305</v>
+        <v>-0.01186215091270229</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01037637654107306</v>
+        <v>0.01037637654107239</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01543191053294826</v>
+        <v>-0.01543191053294733</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00132766977933029</v>
+        <v>0.001327669779330199</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01446376254972542</v>
+        <v>0.01446376254972448</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.005021620520047738</v>
+        <v>-0.005021620520047466</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001270250417328046</v>
+        <v>0.001270250417327927</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01855261482099838</v>
+        <v>0.01855261482099724</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.01314518974061562</v>
+        <v>-0.01314518974061487</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.09410118347796</v>
+        <v>3.094101183479466</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-3.09410118347796</v>
+        <v>-3.094101183479466</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>1.61907524424502e-13</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="F6" t="n">
-        <v>4.04768811061255e-11</v>
+        <v>2.023844055306275e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01575698001207803</v>
+        <v>0.01575698001207688</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01037637654107306</v>
+        <v>0.01037637654107239</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01543191053294826</v>
+        <v>-0.01543191053294733</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.008176238279925323</v>
+        <v>-0.008176238279924853</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01198076103128419</v>
+        <v>0.01198076103128337</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.01575698001207803</v>
+        <v>-0.01575698001207688</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3401,13 +3401,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.00817623827992532</v>
+        <v>-0.008176238279924851</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01670216095027631</v>
+        <v>0.01670216095027526</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.01314518974061562</v>
+        <v>-0.01314518974061487</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>185.6428750708133</v>
+        <v>185.6428750707973</v>
       </c>
       <c r="F7" t="n">
-        <v>46410.71876770334</v>
+        <v>46410.71876769933</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01575698001207803</v>
+        <v>0.01575698001207688</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3493,13 +3493,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3511,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.01575698001207803</v>
+        <v>-0.01575698001207688</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3529,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.05072440278753856</v>
+        <v>-0.05072440278753466</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-185.6428750708134</v>
+        <v>-185.6428750707974</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>185.6428750708134</v>
+        <v>185.6428750707974</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>86.6025403784446</v>
+        <v>86.60254037844444</v>
       </c>
       <c r="F8" t="n">
-        <v>21650.63509461115</v>
+        <v>21650.63509461111</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01037637654107306</v>
+        <v>0.01037637654107239</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01543191053294826</v>
+        <v>-0.01543191053294733</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01855261482099838</v>
+        <v>0.01855261482099724</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001270250417328048</v>
+        <v>0.001270250417327929</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02040838354339362</v>
+        <v>0.02040838354339248</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.089180813320793e-05</v>
+        <v>7.089180813292691e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-86.6025403784447</v>
+        <v>-86.60254037844447</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>86.6025403784447</v>
+        <v>86.60254037844447</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>-124.3839035680058</v>
+        <v>-124.3839035680036</v>
       </c>
       <c r="F9" t="n">
-        <v>-31095.97589200145</v>
+        <v>-31095.97589200091</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01037637654107306</v>
+        <v>0.01037637654107239</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01543191053294826</v>
+        <v>-0.01543191053294733</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06013483678090634</v>
+        <v>0.06013483678090194</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006930127646341633</v>
+        <v>0.006930127646340921</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.01678443355793261</v>
+        <v>-0.01678443355793183</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01670216095027631</v>
+        <v>0.01670216095027526</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.008176238279925318</v>
+        <v>-0.00817623827992485</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01439388337216702</v>
+        <v>0.01439388337216601</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.01107068202613085</v>
+        <v>-0.01107068202613053</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.06013483678090634</v>
+        <v>0.06013483678090194</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>124.3839035680058</v>
+        <v>124.3839035680037</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-124.3839035680058</v>
+        <v>-124.3839035680037</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3853,19 +3853,19 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>-86.60254037844395</v>
+        <v>-86.60254037844427</v>
       </c>
       <c r="F10" t="n">
-        <v>-21650.63509461099</v>
+        <v>-21650.63509461107</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3877,13 +3877,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06013483678090634</v>
+        <v>0.06013483678090194</v>
       </c>
       <c r="N10" t="n">
-        <v>0.006930127646341633</v>
+        <v>0.006930127646340921</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.01678443355793261</v>
+        <v>-0.01678443355793183</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.01014279766493324</v>
+        <v>-0.01014279766493292</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01770962450282176</v>
+        <v>0.01770962450282063</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.05072440278753856</v>
+        <v>-0.05072440278753466</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3913,13 +3913,13 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.01107068202613086</v>
+        <v>-0.01107068202613053</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01439388337216702</v>
+        <v>0.01439388337216601</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.06013483678090634</v>
+        <v>-0.06013483678090194</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>86.6025403784439</v>
+        <v>86.60254037844436</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-86.6025403784439</v>
+        <v>-86.60254037844436</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>142.4751529503453</v>
+        <v>142.4751529503354</v>
       </c>
       <c r="F11" t="n">
-        <v>35618.78823758633</v>
+        <v>35618.78823758385</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.09735868234220449</v>
+        <v>0.09735868234219669</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.05072440278753856</v>
+        <v>-0.05072440278753466</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.09735868234220449</v>
+        <v>-0.09735868234219669</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-142.4751529503454</v>
+        <v>-142.4751529503355</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>142.4751529503454</v>
+        <v>142.4751529503355</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4109,19 +4109,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E12" t="n">
-        <v>-154.0933337512762</v>
+        <v>-154.0933337512698</v>
       </c>
       <c r="F12" t="n">
-        <v>-38523.33343781906</v>
+        <v>-38523.33343781744</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06013483678090634</v>
+        <v>0.06013483678090194</v>
       </c>
       <c r="H12" t="n">
-        <v>0.006930127646341633</v>
+        <v>0.006930127646340921</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01678443355793261</v>
+        <v>-0.01678443355793183</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09735868234220449</v>
+        <v>0.09735868234219669</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -4151,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01439388337216702</v>
+        <v>0.01439388337216601</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.01107068202613085</v>
+        <v>-0.01107068202613053</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06013483678090634</v>
+        <v>0.06013483678090194</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.01153426748111475</v>
+        <v>0.01153426748111386</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.006659312435126748</v>
+        <v>0.006659312435126235</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.09735868234220449</v>
+        <v>0.09735868234219669</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>154.0933337512762</v>
+        <v>154.0933337512697</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-154.0933337512762</v>
+        <v>-154.0933337512697</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4237,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>-272.2094082173839</v>
+        <v>-272.2094082173616</v>
       </c>
       <c r="F13" t="n">
-        <v>-68052.35205434597</v>
+        <v>-68052.3520543404</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005145193090482427</v>
+        <v>0.000514519309048216</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01565677554050815</v>
+        <v>0.015656775540507</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0005145193090482427</v>
+        <v>-0.000514519309048216</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.01565677554050815</v>
+        <v>-0.015656775540507</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>272.209408217384</v>
+        <v>272.2094082173617</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-272.209408217384</v>
+        <v>-272.2094082173617</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E14" t="n">
-        <v>-109.262530770665</v>
+        <v>-109.2625307706595</v>
       </c>
       <c r="F14" t="n">
-        <v>-27315.63269266625</v>
+        <v>-27315.63269266486</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0005145193090482427</v>
+        <v>0.000514519309048216</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.005111801563984978</v>
+        <v>0.005111801563984705</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.006399919298219385</v>
+        <v>-0.006399919298218829</v>
       </c>
       <c r="O14" t="n">
-        <v>0.007029665646177609</v>
+        <v>0.00702966564617685</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0005145193090482427</v>
+        <v>-0.000514519309048216</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.00202765987133946</v>
+        <v>-0.002027659871339357</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.009287828678810253</v>
+        <v>-0.009287828678809317</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.005111801563984978</v>
+        <v>-0.005111801563984705</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>109.262530770665</v>
+        <v>109.2625307706595</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-109.262530770665</v>
+        <v>-109.2625307706595</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -4493,19 +4493,19 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1.61907524424502e-13</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>4.04768811061255e-11</v>
       </c>
       <c r="G15" t="n">
-        <v>0.005111801563984978</v>
+        <v>0.005111801563984705</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.006399919298219385</v>
+        <v>-0.006399919298218829</v>
       </c>
       <c r="I15" t="n">
-        <v>0.007029665646177609</v>
+        <v>0.00702966564617685</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01565677554050815</v>
+        <v>0.015656775540507</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="O15" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -4535,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.009287828678810253</v>
+        <v>-0.009287828678809319</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.00202765987133946</v>
+        <v>-0.002027659871339357</v>
       </c>
       <c r="U15" t="n">
-        <v>0.005111801563984978</v>
+        <v>0.005111801563984705</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.009287828678810253</v>
+        <v>-0.009287828678809317</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.001373105688255575</v>
+        <v>-0.001373105688255563</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01565677554050815</v>
+        <v>0.015656775540507</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4621,19 +4621,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E16" t="n">
-        <v>-30.02922713564882</v>
+        <v>-30.02922713564716</v>
       </c>
       <c r="F16" t="n">
-        <v>-7507.306783912204</v>
+        <v>-7507.306783911789</v>
       </c>
       <c r="G16" t="n">
-        <v>0.005111801563984978</v>
+        <v>0.005111801563984705</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.006399919298219385</v>
+        <v>-0.006399919298218829</v>
       </c>
       <c r="I16" t="n">
-        <v>0.007029665646177609</v>
+        <v>0.00702966564617685</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.007932005006854951</v>
+        <v>-0.00793200500685427</v>
       </c>
       <c r="O16" t="n">
-        <v>0.008568769925563794</v>
+        <v>0.00856876992556288</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.00202765987133946</v>
+        <v>-0.002027659871339357</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.009287828678810253</v>
+        <v>-0.009287828678809317</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.005111801563984978</v>
+        <v>-0.005111801563984705</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4681,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.002584932876099851</v>
+        <v>-0.002584932876099717</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.01138677493814981</v>
+        <v>-0.01138677493814868</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.0132845084551094</v>
+        <v>-0.01328450845510865</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>30.02922713564882</v>
+        <v>30.02922713564715</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-30.02922713564882</v>
+        <v>-30.02922713564715</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4749,19 +4749,19 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.904913843347609e-13</v>
+        <v>-5.869147760388197e-13</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.226228460836902e-10</v>
+        <v>-1.467286940097049e-10</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01565677554050815</v>
+        <v>0.015656775540507</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.007932005006854951</v>
+        <v>-0.00793200500685427</v>
       </c>
       <c r="O17" t="n">
-        <v>0.008568769925563794</v>
+        <v>0.00856876992556288</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.003454769931294883</v>
+        <v>0.003454769931294426</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.008730048425975126</v>
+        <v>-0.008730048425974309</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.01565677554050815</v>
+        <v>-0.015656775540507</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.003454769931294864</v>
+        <v>0.003454769931294413</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.01115370280166365</v>
+        <v>-0.0111537028016626</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.0132845084551094</v>
+        <v>-0.01328450845510865</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>8.810729923425242e-13</v>
+        <v>5.968558980384842e-13</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-8.810729923425242e-13</v>
+        <v>-5.968558980384842e-13</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4877,19 +4877,19 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>-157.658395118412</v>
+        <v>-157.658395118396</v>
       </c>
       <c r="F18" t="n">
-        <v>-39414.598779603</v>
+        <v>-39414.59877959901</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01565677554050815</v>
+        <v>0.015656775540507</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="I18" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.05054266662275473</v>
+        <v>0.05054266662275082</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="O18" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.01565677554050815</v>
+        <v>-0.015656775540507</v>
       </c>
       <c r="U18" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4937,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.05054266662275473</v>
+        <v>-0.05054266662275082</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>157.6583951184121</v>
+        <v>157.6583951183961</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-157.6583951184121</v>
+        <v>-157.6583951183961</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5011,13 +5011,13 @@
         <v>-6.071532165918825e-11</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.007932005006854951</v>
+        <v>-0.00793200500685427</v>
       </c>
       <c r="I19" t="n">
-        <v>0.008568769925563794</v>
+        <v>0.00856876992556288</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -5029,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.05054266662275473</v>
+        <v>0.05054266662275082</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="O19" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -5047,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.01138677493814982</v>
+        <v>-0.01138677493814868</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.002584932876099851</v>
+        <v>-0.002584932876099718</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.01138677493814982</v>
+        <v>-0.01138677493814869</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.004062312080195014</v>
+        <v>-0.004062312080194719</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.05054266662275473</v>
+        <v>0.05054266662275082</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -5133,19 +5133,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E20" t="n">
-        <v>52.55122238416967</v>
+        <v>52.55122238416742</v>
       </c>
       <c r="F20" t="n">
-        <v>13137.80559604242</v>
+        <v>13137.80559604186</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.007932005006854951</v>
+        <v>-0.00793200500685427</v>
       </c>
       <c r="I20" t="n">
-        <v>0.008568769925563794</v>
+        <v>0.00856876992556288</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.06091050489581906</v>
+        <v>0.06091050489581464</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.007727155750851131</v>
+        <v>-0.007727155750850413</v>
       </c>
       <c r="O20" t="n">
-        <v>0.006973120948371539</v>
+        <v>0.006973120948370765</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.01115370280166364</v>
+        <v>-0.0111537028016626</v>
       </c>
       <c r="T20" t="n">
-        <v>0.003454769931294863</v>
+        <v>0.003454769931294412</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.01017847365342187</v>
+        <v>-0.01017847365342086</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.002175322009525624</v>
+        <v>0.002175322009525313</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.06091050489581906</v>
+        <v>0.06091050489581464</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-52.55122238416971</v>
+        <v>-52.55122238416743</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>52.55122238416971</v>
+        <v>52.55122238416743</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>3.23815048849004e-13</v>
+        <v>2.833381677428785e-13</v>
       </c>
       <c r="F21" t="n">
-        <v>8.095376221225099e-11</v>
+        <v>7.083454193571961e-11</v>
       </c>
       <c r="G21" t="n">
-        <v>0.05054266662275473</v>
+        <v>0.05054266662275082</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="I21" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -5285,13 +5285,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.06091050489581906</v>
+        <v>0.06091050489581464</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.007727155750851131</v>
+        <v>-0.007727155750850413</v>
       </c>
       <c r="O21" t="n">
-        <v>0.006973120948371539</v>
+        <v>0.006973120948370765</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.002175322009525621</v>
+        <v>0.00217532200952531</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.01189239240371123</v>
+        <v>-0.0118923924037101</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.05054266662275473</v>
+        <v>-0.05054266662275082</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.002175322009525625</v>
+        <v>0.002175322009525313</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.01017847365342187</v>
+        <v>-0.01017847365342086</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.06091050489581906</v>
+        <v>-0.06091050489581464</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-3.126388037344441e-13</v>
+        <v>-2.842170943040401e-13</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>3.126388037344441e-13</v>
+        <v>2.842170943040401e-13</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5389,19 +5389,19 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>-65.10272033182481</v>
+        <v>-65.10272033181487</v>
       </c>
       <c r="F22" t="n">
-        <v>-16275.6800829562</v>
+        <v>-16275.68008295372</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05054266662275473</v>
+        <v>0.05054266662275082</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="I22" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5413,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.09737080707457024</v>
+        <v>0.09737080707456244</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.01060651122144902</v>
+        <v>-0.01060651122144798</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.05054266662275473</v>
+        <v>-0.05054266662275082</v>
       </c>
       <c r="U22" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5449,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.01060651122144902</v>
+        <v>-0.01060651122144798</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.09737080707457024</v>
+        <v>-0.09737080707456244</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>65.10272033182486</v>
+        <v>65.10272033181491</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>-65.10272033182486</v>
+        <v>-65.10272033181491</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5517,19 +5517,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E23" t="n">
-        <v>53.50696334835786</v>
+        <v>53.50696334835187</v>
       </c>
       <c r="F23" t="n">
-        <v>13376.74083708946</v>
+        <v>13376.74083708797</v>
       </c>
       <c r="G23" t="n">
-        <v>0.06091050489581906</v>
+        <v>0.06091050489581464</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.007727155750851131</v>
+        <v>-0.007727155750850413</v>
       </c>
       <c r="I23" t="n">
-        <v>0.006973120948371539</v>
+        <v>0.006973120948370765</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09737080707457024</v>
+        <v>0.09737080707456244</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.01060651122144902</v>
+        <v>-0.01060651122144798</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -5559,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.01017847365342187</v>
+        <v>-0.01017847365342086</v>
       </c>
       <c r="T23" t="n">
-        <v>0.002175322009525624</v>
+        <v>0.002175322009525313</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06091050489581906</v>
+        <v>0.06091050489581464</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.009185508163299563</v>
+        <v>-0.009185508163298668</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.005303255610724508</v>
+        <v>-0.005303255610723991</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.09737080707457024</v>
+        <v>0.09737080707456244</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>-53.50696334835783</v>
+        <v>-53.50696334835186</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>53.50696334835783</v>
+        <v>53.50696334835186</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5645,10 +5645,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>48.02180217783598</v>
+        <v>48.02180217783349</v>
       </c>
       <c r="F24" t="n">
-        <v>12005.45054445899</v>
+        <v>12005.45054445837</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0005145193090482427</v>
+        <v>0.000514519309048216</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.0005145193090482427</v>
+        <v>0.000514519309048216</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>-48.02180217783599</v>
+        <v>-48.02180217783351</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>48.02180217783599</v>
+        <v>48.02180217783351</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>8.416897434142406</v>
+        <v>8.416897434142326</v>
       </c>
       <c r="F25" t="n">
-        <v>2104.224358535601</v>
+        <v>2104.224358535581</v>
       </c>
       <c r="G25" t="n">
-        <v>0.005021620520047738</v>
+        <v>0.005021620520047466</v>
       </c>
       <c r="H25" t="n">
-        <v>0.008381677031599621</v>
+        <v>0.008381677031599073</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.01186215091270305</v>
+        <v>-0.01186215091270229</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.005111801563984978</v>
+        <v>0.005111801563984705</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.006399919298219385</v>
+        <v>-0.006399919298218829</v>
       </c>
       <c r="O25" t="n">
-        <v>0.007029665646177609</v>
+        <v>0.00702966564617685</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -5815,13 +5815,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.005021620520047738</v>
+        <v>0.005021620520047466</v>
       </c>
       <c r="T25" t="n">
-        <v>0.008381677031599621</v>
+        <v>0.008381677031599073</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.01186215091270305</v>
+        <v>-0.01186215091270229</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5833,13 +5833,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.005111801563984978</v>
+        <v>0.005111801563984705</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.006399919298219385</v>
+        <v>-0.006399919298218829</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.007029665646177609</v>
+        <v>0.00702966564617685</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>-8.416897434142413</v>
+        <v>-8.416897434142356</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>8.416897434142413</v>
+        <v>8.416897434142356</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5907,13 +5907,13 @@
         <v>-2338.104336630532</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01575698001207803</v>
+        <v>0.01575698001207688</v>
       </c>
       <c r="H26" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -5925,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01565677554050815</v>
+        <v>0.015656775540507</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="O26" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.01575698001207803</v>
+        <v>0.01575698001207688</v>
       </c>
       <c r="T26" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.01565677554050815</v>
+        <v>0.015656775540507</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -6029,19 +6029,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>13.00308001941974</v>
+        <v>13.00308001941958</v>
       </c>
       <c r="F27" t="n">
-        <v>3250.770004854935</v>
+        <v>3250.770004854895</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01037637654107306</v>
+        <v>0.01037637654107239</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.01543191053294826</v>
+        <v>-0.01543191053294733</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -6053,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.007932005006854951</v>
+        <v>-0.00793200500685427</v>
       </c>
       <c r="O27" t="n">
-        <v>0.008568769925563794</v>
+        <v>0.00856876992556288</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="T27" t="n">
-        <v>0.01037637654107306</v>
+        <v>0.01037637654107239</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.01543191053294826</v>
+        <v>-0.01543191053294733</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.007932005006854951</v>
+        <v>-0.00793200500685427</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.008568769925563794</v>
+        <v>0.00856876992556288</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -6163,13 +6163,13 @@
         <v>-4240.510511622798</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="H28" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -6181,13 +6181,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.05054266662275473</v>
+        <v>0.05054266662275082</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="O28" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -6199,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -6217,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.05054266662275473</v>
+        <v>0.05054266662275082</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -6285,19 +6285,19 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>72.39569072518705</v>
+        <v>72.39569072518576</v>
       </c>
       <c r="F29" t="n">
-        <v>18098.92268129676</v>
+        <v>18098.92268129644</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06013483678090634</v>
+        <v>0.06013483678090194</v>
       </c>
       <c r="H29" t="n">
-        <v>0.006930127646341633</v>
+        <v>0.006930127646340921</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01678443355793261</v>
+        <v>-0.01678443355793183</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -6309,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.06091050489581906</v>
+        <v>0.06091050489581464</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.007727155750851131</v>
+        <v>-0.007727155750850413</v>
       </c>
       <c r="O29" t="n">
-        <v>0.006973120948371539</v>
+        <v>0.006973120948370765</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.06013483678090634</v>
+        <v>0.06013483678090194</v>
       </c>
       <c r="T29" t="n">
-        <v>0.006930127646341633</v>
+        <v>0.006930127646340921</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.01678443355793261</v>
+        <v>-0.01678443355793183</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.06091050489581906</v>
+        <v>0.06091050489581464</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.007727155750851131</v>
+        <v>-0.007727155750850413</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.006973120948371539</v>
+        <v>0.006973120948370765</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>-72.39569072518771</v>
+        <v>-72.39569072518589</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>72.39569072518771</v>
+        <v>72.39569072518589</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6419,10 +6419,10 @@
         <v>282.9104218675845</v>
       </c>
       <c r="G30" t="n">
-        <v>0.09735868234220449</v>
+        <v>0.09735868234219669</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -6437,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.09737080707457024</v>
+        <v>0.09737080707456244</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.01060651122144902</v>
+        <v>-0.01060651122144798</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -6455,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.09735868234220449</v>
+        <v>0.09735868234219669</v>
       </c>
       <c r="T30" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -6473,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.09737080707457024</v>
+        <v>0.09737080707456244</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.01060651122144902</v>
+        <v>-0.01060651122144798</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>37.32847174831738</v>
+        <v>37.32847174831524</v>
       </c>
       <c r="F31" t="n">
-        <v>9332.117937079345</v>
+        <v>9332.117937078809</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.005111801563984978</v>
+        <v>0.005111801563984705</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.006399919298219385</v>
+        <v>-0.006399919298218829</v>
       </c>
       <c r="O31" t="n">
-        <v>0.007029665646177609</v>
+        <v>0.00702966564617685</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -6601,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.0007998958231782297</v>
+        <v>0.0007998958231781837</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.01058276510922182</v>
+        <v>-0.01058276510922092</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.001967468084983633</v>
+        <v>0.001967468084983237</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-37.3284717483174</v>
+        <v>-37.32847174831525</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>37.3284717483174</v>
+        <v>37.32847174831525</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>-51.50855960893236</v>
+        <v>-51.50855960893036</v>
       </c>
       <c r="F32" t="n">
-        <v>-12877.13990223309</v>
+        <v>-12877.13990223259</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0005145193090482427</v>
+        <v>0.000514519309048216</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6693,13 +6693,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.005021620520047738</v>
+        <v>0.005021620520047466</v>
       </c>
       <c r="N32" t="n">
-        <v>0.008381677031599621</v>
+        <v>0.008381677031599073</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.01186215091270305</v>
+        <v>-0.01186215091270229</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.0002572596545241213</v>
+        <v>-0.000257259654524108</v>
       </c>
       <c r="T32" t="n">
-        <v>0.0002917050292462361</v>
+        <v>0.000291705029246221</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.0003368319543185642</v>
+        <v>-0.0003368319543185468</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.001361014503286957</v>
+        <v>-0.001361014503286902</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.01421514995720669</v>
+        <v>0.0142151499572058</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.005679520930599712</v>
+        <v>0.005679520930599311</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>51.50855960893237</v>
+        <v>51.50855960893038</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>-51.50855960893237</v>
+        <v>-51.50855960893038</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E33" t="n">
-        <v>74.49228351557826</v>
+        <v>74.49228351557475</v>
       </c>
       <c r="F33" t="n">
-        <v>18623.07087889457</v>
+        <v>18623.07087889369</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.01565677554050815</v>
+        <v>0.015656775540507</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="O33" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -6857,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.001784676532928786</v>
+        <v>0.001784676532928702</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.01661246894205172</v>
+        <v>-0.01661246894205048</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-74.49228351557826</v>
+        <v>-74.49228351557474</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>74.49228351557826</v>
+        <v>74.49228351557474</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6925,13 +6925,13 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E34" t="n">
-        <v>-49.7916937173524</v>
+        <v>-49.79169371734914</v>
       </c>
       <c r="F34" t="n">
-        <v>-12447.9234293381</v>
+        <v>-12447.92342933728</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0005145193090482427</v>
+        <v>0.000514519309048216</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.01575698001207803</v>
+        <v>0.01575698001207688</v>
       </c>
       <c r="N34" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.0002301000301536187</v>
+        <v>-0.0002301000301536067</v>
       </c>
       <c r="T34" t="n">
-        <v>0.0004602000603072373</v>
+        <v>0.0004602000603072135</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.001423003014441288</v>
+        <v>-0.001423003014441198</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.01690533770633532</v>
+        <v>0.01690533770633408</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.01307121057345221</v>
+        <v>0.01307121057345139</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>49.79169371735239</v>
+        <v>49.79169371734913</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-49.79169371735239</v>
+        <v>-49.79169371734913</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7053,19 +7053,19 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>34.67476474064762</v>
+        <v>34.67476474064564</v>
       </c>
       <c r="F35" t="n">
-        <v>8668.691185161906</v>
+        <v>8668.69118516141</v>
       </c>
       <c r="G35" t="n">
-        <v>0.005021620520047738</v>
+        <v>0.005021620520047466</v>
       </c>
       <c r="H35" t="n">
-        <v>0.008381677031599621</v>
+        <v>0.008381677031599073</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.01186215091270305</v>
+        <v>-0.01186215091270229</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -7077,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.007932005006854951</v>
+        <v>-0.00793200500685427</v>
       </c>
       <c r="O35" t="n">
-        <v>0.008568769925563794</v>
+        <v>0.00856876992556288</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.003660606016760781</v>
+        <v>0.003660606016760564</v>
       </c>
       <c r="T35" t="n">
-        <v>0.008521167496670194</v>
+        <v>0.00852116749666961</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.01225436554330322</v>
+        <v>-0.01225436554330246</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7113,13 +7113,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.004403636689774658</v>
+        <v>0.004403636689774399</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.01698531903161427</v>
+        <v>-0.01698531903161294</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.002219371005182461</v>
+        <v>-0.002219371005182661</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>-34.67476474064765</v>
+        <v>-34.67476474064566</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>34.67476474064765</v>
+        <v>34.67476474064566</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7181,19 +7181,19 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>-54.1622666166022</v>
+        <v>-54.16226661660009</v>
       </c>
       <c r="F36" t="n">
-        <v>-13540.56665415055</v>
+        <v>-13540.56665415002</v>
       </c>
       <c r="G36" t="n">
-        <v>0.005111801563984978</v>
+        <v>0.005111801563984705</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.006399919298219385</v>
+        <v>-0.006399919298218829</v>
       </c>
       <c r="I36" t="n">
-        <v>0.007029665646177609</v>
+        <v>0.00702966564617685</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -7205,13 +7205,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="N36" t="n">
-        <v>0.01037637654107306</v>
+        <v>0.01037637654107239</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.01543191053294826</v>
+        <v>-0.01543191053294733</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -7223,13 +7223,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.004311905740806748</v>
+        <v>-0.004311905740806522</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.004786526956443842</v>
+        <v>-0.004786526956443255</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.008660387400570721</v>
+        <v>-0.00866038740056997</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7241,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.005472525739733938</v>
+        <v>-0.005472525739733666</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.02189286768611187</v>
+        <v>0.02189286768611054</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.003059881148375805</v>
+        <v>0.003059881148375593</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>54.16226661660221</v>
+        <v>54.16226661660011</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>-54.16226661660221</v>
+        <v>-54.16226661660011</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7309,19 +7309,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E37" t="n">
-        <v>70.70433465812481</v>
+        <v>70.70433465812155</v>
       </c>
       <c r="F37" t="n">
-        <v>17676.0836645312</v>
+        <v>17676.08366453039</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01575698001207803</v>
+        <v>0.01575698001207688</v>
       </c>
       <c r="H37" t="n">
-        <v>0.006287524269800096</v>
+        <v>0.006287524269799625</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -7333,13 +7333,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.05054266662275473</v>
+        <v>0.05054266662275082</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="O37" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01267046835640348</v>
+        <v>0.01267046835640255</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.01128160503535422</v>
+        <v>-0.01128160503535341</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.01307121057345221</v>
+        <v>-0.01307121057345139</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7369,13 +7369,13 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.01436439369854057</v>
+        <v>0.01436439369853956</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0.04932622231702436</v>
+        <v>-0.0493262223170205</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>-70.70433465812482</v>
+        <v>-70.70433465812164</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>70.70433465812482</v>
+        <v>70.70433465812164</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7437,19 +7437,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E38" t="n">
-        <v>-53.57964257480648</v>
+        <v>-53.57964257480307</v>
       </c>
       <c r="F38" t="n">
-        <v>-13394.91064370162</v>
+        <v>-13394.91064370077</v>
       </c>
       <c r="G38" t="n">
-        <v>0.01565677554050815</v>
+        <v>0.015656775540507</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.005833058747515369</v>
+        <v>-0.005833058747514891</v>
       </c>
       <c r="I38" t="n">
-        <v>0.00735694273771955</v>
+        <v>0.007356942737718746</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -7461,13 +7461,13 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="N38" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>-0.01221916923388411</v>
+        <v>-0.01221916923388316</v>
       </c>
       <c r="T38" t="n">
-        <v>0.01139522259157406</v>
+        <v>0.01139522259157325</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.00735694273771955</v>
+        <v>-0.007356942737718746</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.01350282340896349</v>
+        <v>-0.01350282340896247</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.04996019467102628</v>
+        <v>0.04996019467102242</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.01763873269468855</v>
+        <v>0.0176387326946877</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>53.57964257480648</v>
+        <v>53.57964257480313</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>-53.57964257480648</v>
+        <v>-53.57964257480313</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7565,19 +7565,19 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>28.15610657776235</v>
+        <v>28.15610657775992</v>
       </c>
       <c r="F39" t="n">
-        <v>7039.026644440587</v>
+        <v>7039.026644439979</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01314518974061562</v>
+        <v>0.01314518974061487</v>
       </c>
       <c r="H39" t="n">
-        <v>0.01037637654107306</v>
+        <v>0.01037637654107239</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.01543191053294826</v>
+        <v>-0.01543191053294733</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7589,13 +7589,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.06091050489581906</v>
+        <v>0.06091050489581464</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.007727155750851131</v>
+        <v>-0.007727155750850413</v>
       </c>
       <c r="O39" t="n">
-        <v>0.006973120948371539</v>
+        <v>0.006973120948370765</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.02103709055134353</v>
+        <v>0.02103709055134225</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.008166211767289901</v>
+        <v>-0.008166211767289466</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.003059881148375805</v>
+        <v>-0.003059881148375593</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -7625,13 +7625,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.02164043569229558</v>
+        <v>0.02164043569229425</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.03622030902130839</v>
+        <v>-0.03622030902130579</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.04514646958368587</v>
+        <v>0.04514646958368239</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>-28.15610657776233</v>
+        <v>-28.15610657775994</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>28.15610657776233</v>
+        <v>28.15610657775994</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7693,19 +7693,19 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>-60.68092477948768</v>
+        <v>-60.68092477948557</v>
       </c>
       <c r="F40" t="n">
-        <v>-15170.23119487192</v>
+        <v>-15170.23119487139</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0132845084551094</v>
+        <v>0.01328450845510865</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.007932005006854951</v>
+        <v>-0.00793200500685427</v>
       </c>
       <c r="I40" t="n">
-        <v>0.008568769925563794</v>
+        <v>0.00856876992556288</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7717,13 +7717,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.06013483678090634</v>
+        <v>0.06013483678090194</v>
       </c>
       <c r="N40" t="n">
-        <v>0.006930127646341633</v>
+        <v>0.006930127646340921</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.01678443355793261</v>
+        <v>-0.01678443355793183</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.01630164420005709</v>
+        <v>-0.0163016442000558</v>
       </c>
       <c r="T40" t="n">
-        <v>0.006492262708485571</v>
+        <v>0.006492262708485148</v>
       </c>
       <c r="U40" t="n">
-        <v>0.002219371005182461</v>
+        <v>0.002219371005182661</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.01760194973104611</v>
+        <v>-0.01760194973104478</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.03043610313703402</v>
+        <v>0.03043610313703144</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.05205533080501019</v>
+        <v>0.05205533080500672</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>60.68092477948767</v>
+        <v>60.68092477948562</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>-60.68092477948767</v>
+        <v>-60.68092477948562</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7821,19 +7821,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E41" t="n">
-        <v>91.50792162797391</v>
+        <v>91.50792162796985</v>
       </c>
       <c r="F41" t="n">
-        <v>22876.98040699348</v>
+        <v>22876.98040699246</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05072440278753856</v>
+        <v>0.05072440278753466</v>
       </c>
       <c r="H41" t="n">
-        <v>0.01026558587846038</v>
+        <v>0.01026558587845957</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.09737080707457024</v>
+        <v>0.09737080707456244</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.01060651122144902</v>
+        <v>-0.01060651122144798</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.03186646169144293</v>
+        <v>0.03186646169144046</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.04077837552978656</v>
+        <v>-0.04077837552978342</v>
       </c>
       <c r="U41" t="n">
-        <v>-0.01763873269468855</v>
+        <v>-0.0176387326946877</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.03405879669044157</v>
+        <v>0.034058796690439</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.09183447347615746</v>
+        <v>-0.09183447347615002</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-91.50792162797393</v>
+        <v>-91.50792162796984</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>91.50792162797393</v>
+        <v>91.50792162796984</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7949,19 +7949,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E42" t="n">
-        <v>-32.7760556049618</v>
+        <v>-32.77605560495774</v>
       </c>
       <c r="F42" t="n">
-        <v>-8194.013901240449</v>
+        <v>-8194.013901239436</v>
       </c>
       <c r="G42" t="n">
-        <v>0.05054266662275473</v>
+        <v>0.05054266662275082</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.009211452928624199</v>
+        <v>-0.009211452928623378</v>
       </c>
       <c r="I42" t="n">
-        <v>0.007830080323516217</v>
+        <v>0.007830080323515384</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.09735868234220449</v>
+        <v>0.09735868234219669</v>
       </c>
       <c r="N42" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.03084234163449515</v>
+        <v>-0.03084234163449267</v>
       </c>
       <c r="T42" t="n">
-        <v>0.04108724834904707</v>
+        <v>0.04108724834904395</v>
       </c>
       <c r="U42" t="n">
-        <v>-0.007830080323516217</v>
+        <v>-0.007830080323515384</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.03162758615271308</v>
+        <v>-0.03162758615271051</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.09303652288213229</v>
+        <v>0.09303652288212486</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>32.77605560496181</v>
+        <v>32.77605560495772</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>-32.77605560496181</v>
+        <v>-32.77605560495772</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8077,19 +8077,19 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>-84.11045667088723</v>
+        <v>-84.11045667088982</v>
       </c>
       <c r="F43" t="n">
-        <v>-21027.61416772181</v>
+        <v>-21027.61416772246</v>
       </c>
       <c r="G43" t="n">
-        <v>0.06013483678090634</v>
+        <v>0.06013483678090194</v>
       </c>
       <c r="H43" t="n">
-        <v>0.006930127646341633</v>
+        <v>0.006930127646340921</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.01678443355793261</v>
+        <v>-0.01678443355793183</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -8101,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.09737080707457024</v>
+        <v>0.09737080707456244</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.01060651122144902</v>
+        <v>-0.01060651122144798</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -8119,13 +8119,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.04253288704986023</v>
+        <v>0.04253288704985716</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.03775039254313946</v>
+        <v>-0.03775039254313705</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02667965246708064</v>
+        <v>0.02667965246707835</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.04073052012119836</v>
+        <v>0.04073052012119523</v>
       </c>
       <c r="Z43" t="n">
-        <v>-0.06221960641612712</v>
+        <v>-0.06221960641612202</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.06374415627116568</v>
+        <v>0.06374415627116058</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>84.11045667088729</v>
+        <v>84.11045667089002</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>-84.11045667088729</v>
+        <v>-84.11045667089002</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8205,19 +8205,19 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>27.05251197186319</v>
+        <v>27.05251197186513</v>
       </c>
       <c r="F44" t="n">
-        <v>6763.127992965799</v>
+        <v>6763.127992966283</v>
       </c>
       <c r="G44" t="n">
-        <v>0.06091050489581906</v>
+        <v>0.06091050489581464</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.007727155750851131</v>
+        <v>-0.007727155750850413</v>
       </c>
       <c r="I44" t="n">
-        <v>0.006973120948371539</v>
+        <v>0.006973120948370765</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.09735868234220449</v>
+        <v>0.09735868234219669</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0133186248702535</v>
+        <v>0.01331862487025247</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -8247,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.03927006920352347</v>
+        <v>-0.03927006920352039</v>
       </c>
       <c r="T44" t="n">
-        <v>0.03284571162971422</v>
+        <v>0.03284571162971182</v>
       </c>
       <c r="U44" t="n">
-        <v>0.03460410164576246</v>
+        <v>0.03460410164576015</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8265,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>-0.03869037251841212</v>
+        <v>-0.03869037251840899</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.06400662689952878</v>
+        <v>0.06400662689952367</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.0637362187706161</v>
+        <v>0.06373621877061099</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>-27.05251197186317</v>
+        <v>-27.05251197186521</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>27.05251197186317</v>
+        <v>27.05251197186521</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>

--- a/outputs/validation_truss_nodal_loads.xlsx
+++ b/outputs/validation_truss_nodal_loads.xlsx
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-293.4177992573159</v>
+        <v>-293.4177992573158</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>293.4177992573159</v>
+        <v>293.4177992573158</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>3.23815048849004e-13</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>-3.23815048849004e-13</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.094101183479466</v>
+        <v>3.094101183479459</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-3.094101183479466</v>
+        <v>-3.094101183479459</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-185.6428750707974</v>
+        <v>-185.6428750707973</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>185.6428750707974</v>
+        <v>185.6428750707973</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-86.60254037844447</v>
+        <v>-86.60254037844444</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>86.60254037844447</v>
+        <v>86.60254037844444</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>124.3839035680037</v>
+        <v>124.3839035680036</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-124.3839035680037</v>
+        <v>-124.3839035680036</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>86.60254037844436</v>
+        <v>86.60254037844427</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-86.60254037844436</v>
+        <v>-86.60254037844427</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-142.4751529503355</v>
+        <v>-142.4751529503354</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>142.4751529503355</v>
+        <v>142.4751529503354</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>154.0933337512697</v>
+        <v>154.0933337512698</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-154.0933337512697</v>
+        <v>-154.0933337512698</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>272.2094082173617</v>
+        <v>272.2094082173616</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-272.2094082173617</v>
+        <v>-272.2094082173616</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-1.61907524424502e-13</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>1.61907524424502e-13</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>30.02922713564715</v>
+        <v>30.02922713564716</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-30.02922713564715</v>
+        <v>-30.02922713564716</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>5.968558980384842e-13</v>
+        <v>5.869147760388197e-13</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-5.968558980384842e-13</v>
+        <v>-5.869147760388197e-13</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>157.6583951183961</v>
+        <v>157.658395118396</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-157.6583951183961</v>
+        <v>-157.658395118396</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>2.42861286636753e-13</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-2.42861286636753e-13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-52.55122238416743</v>
+        <v>-52.55122238416742</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>52.55122238416743</v>
+        <v>52.55122238416742</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-2.842170943040401e-13</v>
+        <v>-2.833381677428785e-13</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.842170943040401e-13</v>
+        <v>2.833381677428785e-13</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>65.10272033181491</v>
+        <v>65.10272033181487</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>-65.10272033181491</v>
+        <v>-65.10272033181487</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>-53.50696334835186</v>
+        <v>-53.50696334835187</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>53.50696334835186</v>
+        <v>53.50696334835187</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>-48.02180217783351</v>
+        <v>-48.02180217783349</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>48.02180217783351</v>
+        <v>48.02180217783349</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>-8.416897434142356</v>
+        <v>-8.416897434142326</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>8.416897434142356</v>
+        <v>8.416897434142326</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>9.352417346522088</v>
+        <v>9.352417346522127</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>-9.352417346522088</v>
+        <v>-9.352417346522127</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>-13.00308001941971</v>
+        <v>-13.00308001941958</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>13.00308001941971</v>
+        <v>13.00308001941958</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>16.96204204649166</v>
+        <v>16.96204204649119</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>-16.96204204649166</v>
+        <v>-16.96204204649119</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>-72.39569072518589</v>
+        <v>-72.39569072518576</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>72.39569072518589</v>
+        <v>72.39569072518576</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>-1.131641687470619</v>
+        <v>-1.131641687470338</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.131641687470619</v>
+        <v>1.131641687470338</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-37.32847174831525</v>
+        <v>-37.32847174831524</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>37.32847174831525</v>
+        <v>37.32847174831524</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>51.50855960893038</v>
+        <v>51.50855960893036</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>-51.50855960893038</v>
+        <v>-51.50855960893036</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-74.49228351557474</v>
+        <v>-74.49228351557475</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>74.49228351557474</v>
+        <v>74.49228351557475</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>49.79169371734913</v>
+        <v>49.79169371734914</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-49.79169371734913</v>
+        <v>-49.79169371734914</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>-34.67476474064566</v>
+        <v>-34.67476474064564</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>34.67476474064566</v>
+        <v>34.67476474064564</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>54.16226661660011</v>
+        <v>54.16226661660009</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>-54.16226661660011</v>
+        <v>-54.16226661660009</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>-70.70433465812164</v>
+        <v>-70.70433465812155</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>70.70433465812164</v>
+        <v>70.70433465812155</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>53.57964257480313</v>
+        <v>53.57964257480307</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>-53.57964257480313</v>
+        <v>-53.57964257480307</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>-28.15610657775994</v>
+        <v>-28.15610657775992</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>28.15610657775994</v>
+        <v>28.15610657775992</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>60.68092477948562</v>
+        <v>60.68092477948557</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>-60.68092477948562</v>
+        <v>-60.68092477948557</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-91.50792162796984</v>
+        <v>-91.50792162796985</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>91.50792162796984</v>
+        <v>91.50792162796985</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>32.77605560495772</v>
+        <v>32.77605560495774</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>-32.77605560495772</v>
+        <v>-32.77605560495774</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>84.11045667089002</v>
+        <v>84.11045667088982</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>-84.11045667089002</v>
+        <v>-84.11045667088982</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>-27.05251197186521</v>
+        <v>-27.05251197186513</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>27.05251197186521</v>
+        <v>27.05251197186513</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
